--- a/基本設計/12_プロジェクト_API基本設計書.xlsx
+++ b/基本設計/12_プロジェクト_API基本設計書.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R47bc5c5439014d7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rb15d93a0afc046c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_API一覧" sheetId="19" r:id="R5379503b350c4554"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_エラーコード" sheetId="22" r:id="Rda1ec3d53daf4918"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_API主要項目処理" sheetId="23" r:id="R952a49aefd6e44e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_API処理・権限" sheetId="24" r:id="R98e3cf78ef2d482c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_API項目定義" sheetId="25" r:id="Rb2ac3b7df99741d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_APIサンプル" sheetId="26" r:id="Rf193f4d7df644c4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_API権限対応" sheetId="27" r:id="R60e2a7081af8450e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R6f9bbd7291b24d28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R54f1872e3db54a0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_API一覧" sheetId="19" r:id="R30e8e5593f9d4a67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_エラーコード" sheetId="22" r:id="Ra6341c1a96eb4697"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_API主要項目処理" sheetId="23" r:id="R2c4327abb191462e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_API処理・権限" sheetId="24" r:id="Rf44e0024dba84524"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_API項目定義" sheetId="25" r:id="R01cba4df348e4f52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_APIサンプル" sheetId="26" r:id="R5cfdfaf9741c4c98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_API権限対応" sheetId="27" r:id="Rb739cd9b1bb546a9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1297,10 +1297,7 @@
       <x:c r="F16" s="196"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.8 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
+      <x:c r="A17"/>
       <x:c r="C17"/>
       <x:c r="D17"/>
       <x:c r="E17"/>
@@ -1316,25 +1313,22 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
-      <x:c r="B19" s="240" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.7 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
-      <x:c r="C19" s="240"/>
-      <x:c r="D19" s="240"/>
-      <x:c r="E19" s="240"/>
-      <x:c r="F19" s="240"/>
-      <x:c r="G19" s="240"/>
-      <x:c r="H19" s="240"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
     </x:row>
     <x:row r="20">
-      <x:c r="B20" s="240"/>
-      <x:c r="C20" s="240"/>
-      <x:c r="D20" s="240"/>
-      <x:c r="E20" s="240"/>
-      <x:c r="F20" s="240"/>
-      <x:c r="G20" s="240"/>
-      <x:c r="H20" s="240"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
     </x:row>
     <x:row r="21">
       <x:c r="B21" s="240"/>
@@ -3470,17 +3464,15 @@
       <x:c r="I16" s="64"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="88" t="str">
-        <x:v>Class名、Method名、SQLは詳細設計で定義する。ただし本SheetのURL、I/O、権限、Data範囲、Error契約はPG判断で変更しない。</x:v>
-      </x:c>
-      <x:c r="B17" s="89"/>
-      <x:c r="C17" s="89"/>
-      <x:c r="D17" s="89"/>
-      <x:c r="E17" s="89"/>
-      <x:c r="F17" s="89"/>
-      <x:c r="G17" s="89"/>
-      <x:c r="H17" s="89"/>
-      <x:c r="I17" s="90"/>
+      <x:c r="A17"/>
+      <x:c r="B17"/>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
+      <x:c r="E17"/>
+      <x:c r="F17"/>
+      <x:c r="G17"/>
+      <x:c r="H17"/>
+      <x:c r="I17"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="91"/>

--- a/基本設計/12_プロジェクト_API基本設計書.xlsx
+++ b/基本設計/12_プロジェクト_API基本設計書.xlsx
@@ -2,15 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R6f9bbd7291b24d28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R54f1872e3db54a0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_API一覧" sheetId="19" r:id="R30e8e5593f9d4a67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_エラーコード" sheetId="22" r:id="Ra6341c1a96eb4697"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_API主要項目処理" sheetId="23" r:id="R2c4327abb191462e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_API処理・権限" sheetId="24" r:id="Rf44e0024dba84524"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_API項目定義" sheetId="25" r:id="R01cba4df348e4f52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_APIサンプル" sheetId="26" r:id="R5cfdfaf9741c4c98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_API権限対応" sheetId="27" r:id="Rb739cd9b1bb546a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R025771451bd747c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R4afdd97bc1564f25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_API一覧" sheetId="19" r:id="R01837be51e694ce9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_エラーコード" sheetId="22" r:id="R5bc2d37936684acb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_API処理・権限" sheetId="24" r:id="R779756897d4b4c93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_API項目定義" sheetId="25" r:id="R8460e39aeff84edc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_APIサンプル" sheetId="26" r:id="R59670955486242c2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -24,7 +22,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="25">
+  <x:fonts count="27">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -163,8 +161,19 @@
       <x:color rgb="FF1F1F1F"/>
       <x:name val="Yu Gothic"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF18283A"/>
+      <x:name val="Yu Gothic"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="17"/>
+      <x:color rgb="FF193C61"/>
+      <x:name val="Yu Gothic"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="29">
+  <x:fills count="31">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -306,8 +315,18 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF234F77"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF1F5FA"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="8">
+  <x:borders count="9">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -365,11 +384,25 @@
         <x:color rgb="FFA6A6A6"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="241">
+  <x:cellXfs count="257">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -867,6 +900,50 @@
     <x:xf numFmtId="0" fontId="24" fillId="28" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="30" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1235,8 +1312,8 @@
     </x:row>
     <x:row r="11">
       <x:c r="B11"/>
-      <x:c r="C11" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="C11" s="203" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="D11"/>
       <x:c r="E11"/>
@@ -1245,8 +1322,8 @@
       <x:c r="H11"/>
     </x:row>
     <x:row r="12">
-      <x:c r="C12" s="235" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="C12" s="242" t="str">
+        <x:v>Document ID</x:v>
       </x:c>
       <x:c r="D12" s="196" t="str">
         <x:v>CW-BD-API-PRJ</x:v>
@@ -1258,8 +1335,8 @@
       <x:c r="C13" s="235" t="str">
         <x:v>版数</x:v>
       </x:c>
-      <x:c r="D13" s="196" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="D13" s="243" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="E13" s="196"/>
       <x:c r="F13" s="196"/>
@@ -1268,8 +1345,8 @@
       <x:c r="C14" s="235" t="str">
         <x:v>改訂日</x:v>
       </x:c>
-      <x:c r="D14" s="196" t="str">
-        <x:v>2026-08-12</x:v>
+      <x:c r="D14" s="243" t="str">
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="E14" s="196"/>
       <x:c r="F14" s="196"/>
@@ -1290,24 +1367,29 @@
       <x:c r="C16" s="235" t="str">
         <x:v>状態</x:v>
       </x:c>
-      <x:c r="D16" s="196" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="D16" s="243" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="E16" s="196"/>
       <x:c r="F16" s="196"/>
     </x:row>
-    <x:row r="17">
-      <x:c r="A17"/>
-      <x:c r="C17"/>
-      <x:c r="D17"/>
+    <x:row r="17" ht="26" customHeight="1">
+      <x:c r="A17" s="245"/>
+      <x:c r="B17" s="245"/>
+      <x:c r="C17" s="245"/>
+      <x:c r="D17" s="245"/>
       <x:c r="E17"/>
       <x:c r="F17"/>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18"/>
-      <x:c r="B18"/>
-      <x:c r="C18"/>
-      <x:c r="D18"/>
+    <x:row r="18" ht="26" customHeight="1">
+      <x:c r="A18" s="245"/>
+      <x:c r="B18" s="245"/>
+      <x:c r="C18" s="245" t="str">
+        <x:v>Baseline ID</x:v>
+      </x:c>
+      <x:c r="D18" s="245" t="str">
+        <x:v>BL-2026-09-24</x:v>
+      </x:c>
       <x:c r="E18"/>
       <x:c r="F18"/>
     </x:row>
@@ -1415,41 +1497,29 @@
       <x:c r="G2" s="172"/>
       <x:c r="H2" s="172"/>
     </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="174" t="str">
-        <x:v>システム名</x:v>
-      </x:c>
-      <x:c r="B3" s="139" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="C3" s="139"/>
-      <x:c r="D3" s="174" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="E3" s="139" t="str">
-        <x:v>DOCUMENT-REVISION</x:v>
-      </x:c>
-      <x:c r="F3" s="139"/>
-      <x:c r="G3" s="139"/>
-      <x:c r="H3" s="139"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="174" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="139" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="C4" s="139"/>
-      <x:c r="D4" s="174" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
-      <x:c r="E4" s="139" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
-      <x:c r="F4" s="139"/>
-      <x:c r="G4" s="139"/>
-      <x:c r="H4" s="139"/>
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="246" t="str">
+        <x:v>システム名：Company WorkHub</x:v>
+      </x:c>
+      <x:c r="B3" s="63"/>
+      <x:c r="C3" s="63"/>
+      <x:c r="D3" s="246"/>
+      <x:c r="E3" s="63"/>
+      <x:c r="F3" s="63"/>
+      <x:c r="G3" s="63"/>
+      <x:c r="H3" s="63"/>
+    </x:row>
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="246" t="str">
+        <x:v>版数：Ver.2.5    改訂日：2026-09-24    Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="B4" s="63"/>
+      <x:c r="C4" s="63"/>
+      <x:c r="D4" s="246"/>
+      <x:c r="E4" s="63"/>
+      <x:c r="F4" s="63"/>
+      <x:c r="G4" s="63"/>
+      <x:c r="H4" s="63"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5"/>
@@ -1481,7 +1551,7 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="C7" s="181" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>改訂内容</x:v>
       </x:c>
       <x:c r="D7" s="181" t="str">
         <x:v>作成者</x:v>
@@ -1519,7 +1589,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G8" s="67" t="str">
-        <x:v>作成済</x:v>
+        <x:v>作成中</x:v>
       </x:c>
       <x:c r="H8" s="67" t="str">
         <x:v>基本設計初版</x:v>
@@ -1545,7 +1615,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G9" s="67" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H9" s="67" t="str">
         <x:v>Leader Review後Baseline化</x:v>
@@ -1571,7 +1641,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G10" s="67" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H10" s="67" t="str">
         <x:v>Review指摘対応</x:v>
@@ -1597,7 +1667,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G11" s="67" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H11" s="67" t="str">
         <x:v>再監査指摘対応</x:v>
@@ -1623,7 +1693,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G12" s="67" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H12" s="67" t="str">
         <x:v>再監査第2回指摘対応</x:v>
@@ -1648,8 +1718,8 @@
       <x:c r="F13" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G13" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G13" s="203" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H13" t="str">
         <x:v>再監査残項対応</x:v>
@@ -1674,8 +1744,8 @@
       <x:c r="F14" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G14" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G14" s="203" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H14" t="str">
         <x:v>再Review指摘対応</x:v>
@@ -1700,25 +1770,127 @@
       <x:c r="F15" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G15" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G15" s="203" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H15" t="str">
         <x:v>最大10回の反復監査対応</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>2.0</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>七項目Review指摘対応：画面・API・DB項目、論理削除、認証限流、日報関連Task、Baseline判定を整合</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G16" t="str">
+        <x:v>レビュー済</x:v>
+      </x:c>
+      <x:c r="H16" t="str">
+        <x:v>Leader最終承認待ち</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="110" customHeight="1">
+      <x:c r="A17" s="241" t="str">
+        <x:v>Ver.2.3</x:v>
+      </x:c>
+      <x:c r="B17" s="241" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="C17" s="241" t="str">
+        <x:v>内容・関連Reviewの既確定仕様を整合。業務未決事項は承認待ちとして管理。</x:v>
+      </x:c>
+      <x:c r="D17" s="241" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E17" s="241" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F17" s="241" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G17" s="241" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H17" s="241" t="str">
+        <x:v>2026-09-18指摘対応。正式承認を示すものではない。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="40" customHeight="1">
+      <x:c r="A18" s="241" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="B18" s="241" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="C18" s="241" t="str">
+        <x:v>待確認12項目の方針選定、業務/API/DB/画面/運用を連動修正。章立て維持。</x:v>
+      </x:c>
+      <x:c r="D18" s="241" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E18" s="241" t="str">
+        <x:v>未実施</x:v>
+      </x:c>
+      <x:c r="F18" s="241" t="str">
+        <x:v>未承認</x:v>
+      </x:c>
+      <x:c r="G18" s="241" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H18" s="241" t="str">
+        <x:v>一般社内管理Systemの範囲。旧版はBackup保管。</x:v>
+      </x:c>
+      <x:c r="I18" s="241"/>
+      <x:c r="J18" s="241"/>
+      <x:c r="K18" s="241"/>
+      <x:c r="L18" s="241"/>
+    </x:row>
+    <x:row r="19" ht="100" customHeight="1">
+      <x:c r="A19" s="245" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="B19" s="245" t="str">
+        <x:v>2026-09-24</x:v>
+      </x:c>
+      <x:c r="C19" s="245" t="str">
+        <x:v>共通規則・正本参照・構成・文書管理を統合修正。Baseline承認前の最終整合修正。</x:v>
+      </x:c>
+      <x:c r="D19" s="245" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="E19" s="245" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F19" s="245" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G19" s="245" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="H19" s="245" t="str">
+        <x:v>BL-2026-09-24。責任者・Review者・承認者はProject Leaderが記入。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H2"/>
-    <x:mergeCell ref="A3:B3"/>
-    <x:mergeCell ref="C3:D3"/>
-    <x:mergeCell ref="E3:F3"/>
-    <x:mergeCell ref="G3:H3"/>
-    <x:mergeCell ref="A4:B4"/>
-    <x:mergeCell ref="C4:D4"/>
-    <x:mergeCell ref="E4:F4"/>
-    <x:mergeCell ref="G4:H4"/>
     <x:mergeCell ref="A6:H6"/>
+    <x:mergeCell ref="A3:H3"/>
+    <x:mergeCell ref="A4:H4"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1767,36 +1939,28 @@
       <x:c r="A3" s="62" t="str">
         <x:v>システム名</x:v>
       </x:c>
-      <x:c r="B3" s="63" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
+      <x:c r="B3" s="63" t="str"/>
       <x:c r="C3" s="63"/>
       <x:c r="D3" s="63"/>
-      <x:c r="E3" s="62" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="F3" s="63" t="str">
-        <x:v>CW-BD-API-PRJ-LIST</x:v>
-      </x:c>
+      <x:c r="E3" s="246" t="str">
+        <x:v>章ID</x:v>
+      </x:c>
+      <x:c r="F3" s="63" t="str"/>
       <x:c r="G3" s="63"/>
       <x:c r="H3" s="63"/>
       <x:c r="I3" s="63"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="62" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="63" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
+      <x:c r="A4" s="246" t="str">
+        <x:v>版数：Ver.2.5</x:v>
+      </x:c>
+      <x:c r="B4" s="63"/>
       <x:c r="C4" s="63"/>
       <x:c r="D4" s="63"/>
-      <x:c r="E4" s="62" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
-      <x:c r="F4" s="63" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
+      <x:c r="E4" s="246" t="str">
+        <x:v>改訂日：2026-09-24</x:v>
+      </x:c>
+      <x:c r="F4" s="63"/>
       <x:c r="G4" s="63"/>
       <x:c r="H4" s="63"/>
       <x:c r="I4" s="63"/>
@@ -1854,7 +2018,7 @@
         <x:v>Error Code</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="30" customHeight="1">
+    <x:row r="8" ht="39" customHeight="1">
       <x:c r="A8" s="67" t="str">
         <x:v>API-PRJ-001</x:v>
       </x:c>
@@ -1868,22 +2032,22 @@
         <x:v>PJ検索</x:v>
       </x:c>
       <x:c r="E8" s="67" t="str">
-        <x:v>全員</x:v>
+        <x:v>02／13_API権限対応：API-PRJ-001</x:v>
       </x:c>
       <x:c r="F8" s="67" t="str">
-        <x:v>query: code,name,managerId,status,startFrom,startTo,endFrom,endTo,mine,page,size,sort</x:v>
+        <x:v>23_API項目定義：API-PRJ-001 Request</x:v>
       </x:c>
       <x:c r="G8" s="67" t="str">
-        <x:v>Page&lt;ProjectSummary&gt;</x:v>
+        <x:v>23_API項目定義：API-PRJ-001 Response（正本）</x:v>
       </x:c>
       <x:c r="H8" s="67" t="str">
         <x:v>SCR-008</x:v>
       </x:c>
       <x:c r="I8" s="67" t="str">
-        <x:v>COMMON-4000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F8／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="39" customHeight="1">
       <x:c r="A9" s="67" t="str">
         <x:v>API-PRJ-002</x:v>
       </x:c>
@@ -1897,22 +2061,22 @@
         <x:v>PJ詳細</x:v>
       </x:c>
       <x:c r="E9" s="67" t="str">
-        <x:v>関係者</x:v>
+        <x:v>02／13_API権限対応：API-PRJ-002</x:v>
       </x:c>
       <x:c r="F9" s="67" t="str">
-        <x:v>path: id Long</x:v>
+        <x:v>23_API項目定義：API-PRJ-002 Request</x:v>
       </x:c>
       <x:c r="G9" s="67" t="str">
-        <x:v>ProjectDetail + members[] + taskSummary</x:v>
+        <x:v>23_API項目定義：API-PRJ-002 Response（正本）</x:v>
       </x:c>
       <x:c r="H9" s="67" t="str">
         <x:v>SCR-010, SCR-011</x:v>
       </x:c>
       <x:c r="I9" s="67" t="str">
-        <x:v>COMMON-4040/AUTH-4006</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F9／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="39" customHeight="1">
       <x:c r="A10" s="67" t="str">
         <x:v>API-PRJ-003</x:v>
       </x:c>
@@ -1926,22 +2090,22 @@
         <x:v>PJ登録</x:v>
       </x:c>
       <x:c r="E10" s="67" t="str">
-        <x:v>管理者</x:v>
+        <x:v>02／13_API権限対応：API-PRJ-003</x:v>
       </x:c>
       <x:c r="F10" s="67" t="str">
-        <x:v>body: projectCode,name,managerId,startDate,endDate,status,customerName,budgetHours,description; header: X-Idempotency-Key</x:v>
+        <x:v>23_API項目定義：API-PRJ-003 Request</x:v>
       </x:c>
       <x:c r="G10" s="67" t="str">
-        <x:v>id,projectCode,version</x:v>
+        <x:v>23_API項目定義：API-PRJ-003 Response（正本）</x:v>
       </x:c>
       <x:c r="H10" s="67" t="str">
         <x:v>SCR-009</x:v>
       </x:c>
       <x:c r="I10" s="67" t="str">
-        <x:v>PRJ-4001, PRJ-4002,COMMON-4090</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F10／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="39" customHeight="1">
       <x:c r="A11" s="67" t="str">
         <x:v>API-PRJ-004</x:v>
       </x:c>
@@ -1955,22 +2119,22 @@
         <x:v>PJ更新</x:v>
       </x:c>
       <x:c r="E11" s="67" t="str">
-        <x:v>管理者/担当PM</x:v>
+        <x:v>02／13_API権限対応：API-PRJ-004</x:v>
       </x:c>
       <x:c r="F11" s="67" t="str">
-        <x:v>path: id; body: name,managerId,startDate,endDate,customerName,budgetHours,description,version</x:v>
+        <x:v>23_API項目定義：API-PRJ-004 Request</x:v>
       </x:c>
       <x:c r="G11" s="67" t="str">
-        <x:v>id,version</x:v>
+        <x:v>23_API項目定義：API-PRJ-004 Response（正本）</x:v>
       </x:c>
       <x:c r="H11" s="67" t="str">
         <x:v>SCR-010</x:v>
       </x:c>
       <x:c r="I11" s="67" t="str">
-        <x:v>PRJ-4001, PRJ-4002,COMMON-4040, COMMON-4090</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F11／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="39" customHeight="1">
       <x:c r="A12" s="67" t="str">
         <x:v>API-PRJ-005</x:v>
       </x:c>
@@ -1984,22 +2148,22 @@
         <x:v>PJ状態変更</x:v>
       </x:c>
       <x:c r="E12" s="67" t="str">
-        <x:v>管理者/担当PM</x:v>
+        <x:v>02／13_API権限対応：API-PRJ-005</x:v>
       </x:c>
       <x:c r="F12" s="67" t="str">
-        <x:v>path: id; body: status,version</x:v>
+        <x:v>23_API項目定義：API-PRJ-005 Request</x:v>
       </x:c>
       <x:c r="G12" s="67" t="str">
-        <x:v>id,status,progress,version</x:v>
+        <x:v>23_API項目定義：API-PRJ-005 Response（正本）</x:v>
       </x:c>
       <x:c r="H12" s="67" t="str">
         <x:v>SCR-010, SCR-011</x:v>
       </x:c>
       <x:c r="I12" s="67" t="str">
-        <x:v>PRJ-4003,COMMON-4090</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F12／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="39" customHeight="1">
       <x:c r="A13" s="67" t="str">
         <x:v>API-PRJ-006</x:v>
       </x:c>
@@ -2013,22 +2177,22 @@
         <x:v>Member検索</x:v>
       </x:c>
       <x:c r="E13" s="67" t="str">
-        <x:v>関係者</x:v>
+        <x:v>02／13_API権限対応：API-PRJ-006</x:v>
       </x:c>
       <x:c r="F13" s="67" t="str">
-        <x:v>path: id; query: status,page,size</x:v>
+        <x:v>23_API項目定義：API-PRJ-006 Request</x:v>
       </x:c>
       <x:c r="G13" s="67" t="str">
-        <x:v>Page&lt;ProjectMember&gt;</x:v>
+        <x:v>23_API項目定義：API-PRJ-006 Response（正本）</x:v>
       </x:c>
       <x:c r="H13" s="67" t="str">
         <x:v>SCR-011, SCR-012</x:v>
       </x:c>
       <x:c r="I13" s="67" t="str">
-        <x:v>AUTH-4006</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F13／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="39" customHeight="1">
       <x:c r="A14" s="67" t="str">
         <x:v>API-PRJ-007</x:v>
       </x:c>
@@ -2042,22 +2206,22 @@
         <x:v>Member追加</x:v>
       </x:c>
       <x:c r="E14" s="67" t="str">
-        <x:v>管理者/担当PM</x:v>
+        <x:v>02／13_API権限対応：API-PRJ-007</x:v>
       </x:c>
       <x:c r="F14" s="67" t="str">
-        <x:v>path: id; body: employeeId,projectRole,joinedDate; header: X-Idempotency-Key</x:v>
+        <x:v>23_API項目定義：API-PRJ-007 Request</x:v>
       </x:c>
       <x:c r="G14" s="67" t="str">
-        <x:v>id,employeeId,version</x:v>
+        <x:v>23_API項目定義：API-PRJ-007 Response（正本）</x:v>
       </x:c>
       <x:c r="H14" s="67" t="str">
         <x:v>SCR-012</x:v>
       </x:c>
       <x:c r="I14" s="67" t="str">
-        <x:v>PRJ-4004,COMMON-4090</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="30" customHeight="1">
+        <x:v>22_API処理・権限!F14／21_エラーコード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="39" customHeight="1">
       <x:c r="A15" s="67" t="str">
         <x:v>API-PRJ-008</x:v>
       </x:c>
@@ -2071,19 +2235,19 @@
         <x:v>Member削除</x:v>
       </x:c>
       <x:c r="E15" s="67" t="str">
-        <x:v>管理者/担当PM</x:v>
+        <x:v>02／13_API権限対応：API-PRJ-008</x:v>
       </x:c>
       <x:c r="F15" s="67" t="str">
-        <x:v>path: id,employeeId; query: version</x:v>
+        <x:v>23_API項目定義：API-PRJ-008 Request</x:v>
       </x:c>
       <x:c r="G15" s="67" t="str">
-        <x:v>204 No Content</x:v>
+        <x:v>23_API項目定義：API-PRJ-008 Response（正本）</x:v>
       </x:c>
       <x:c r="H15" s="67" t="str">
         <x:v>SCR-012</x:v>
       </x:c>
       <x:c r="I15" s="67" t="str">
-        <x:v>PRJ-4005,COMMON-4090</x:v>
+        <x:v>22_API処理・権限!F15／21_エラーコード</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -2525,353 +2689,283 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="52" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="54" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="30" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="159" t="str">
-        <x:v>業務エラーコード</x:v>
-      </x:c>
-      <x:c r="B1" s="159"/>
-      <x:c r="C1" s="159"/>
-      <x:c r="D1" s="159"/>
-      <x:c r="E1" s="159"/>
-      <x:c r="F1" s="159"/>
-      <x:c r="G1" s="159"/>
-      <x:c r="H1" s="159"/>
+      <x:c r="A1" s="250" t="str">
+        <x:v>21_エラーコード</x:v>
+      </x:c>
+      <x:c r="B1" s="249"/>
+      <x:c r="C1" s="249"/>
+      <x:c r="D1" s="249"/>
+      <x:c r="E1" s="249"/>
+      <x:c r="F1" s="249"/>
+      <x:c r="G1" s="249"/>
+      <x:c r="H1" s="249"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="159"/>
-      <x:c r="B2" s="159"/>
-      <x:c r="C2" s="159"/>
-      <x:c r="D2" s="159"/>
-      <x:c r="E2" s="159"/>
-      <x:c r="F2" s="159"/>
-      <x:c r="G2" s="159"/>
-      <x:c r="H2" s="159"/>
+      <x:c r="A2" s="249"/>
+      <x:c r="B2" s="249"/>
+      <x:c r="C2" s="249"/>
+      <x:c r="D2" s="249"/>
+      <x:c r="E2" s="249"/>
+      <x:c r="F2" s="249"/>
+      <x:c r="G2" s="249"/>
+      <x:c r="H2" s="249"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="161" t="str">
-        <x:v>システム名</x:v>
-      </x:c>
-      <x:c r="B3" s="139" t="str">
+      <x:c r="A3" s="249" t="str">
         <x:v>Company WorkHub</x:v>
       </x:c>
-      <x:c r="C3" s="139"/>
-      <x:c r="D3" s="161" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="E3" s="139" t="str">
-        <x:v>CW-BD-053</x:v>
-      </x:c>
-      <x:c r="F3" s="139"/>
-      <x:c r="G3" s="139"/>
-      <x:c r="H3" s="139"/>
+      <x:c r="B3" s="249"/>
+      <x:c r="C3" s="249"/>
+      <x:c r="D3" s="249"/>
+      <x:c r="E3" s="249"/>
+      <x:c r="F3" s="249"/>
+      <x:c r="G3" s="249"/>
+      <x:c r="H3" s="249"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="161" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="139" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="C4" s="139"/>
-      <x:c r="D4" s="161" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
-      <x:c r="E4" s="139" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
-      <x:c r="F4" s="139"/>
-      <x:c r="G4" s="139"/>
-      <x:c r="H4" s="139"/>
+      <x:c r="A4" s="249"/>
+      <x:c r="B4" s="249"/>
+      <x:c r="C4" s="249"/>
+      <x:c r="D4" s="249"/>
+      <x:c r="E4" s="249"/>
+      <x:c r="F4" s="249"/>
+      <x:c r="G4" s="249"/>
+      <x:c r="H4" s="249"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="249" t="str">
+        <x:v>BL-2026-09-24 / Review中</x:v>
+      </x:c>
+      <x:c r="B5" s="249"/>
+      <x:c r="C5" s="249"/>
+      <x:c r="D5" s="249"/>
+      <x:c r="E5" s="249"/>
+      <x:c r="F5" s="249"/>
+      <x:c r="G5" s="249"/>
+      <x:c r="H5" s="249"/>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
-      <x:c r="A6" s="162" t="str">
-        <x:v>1. Error Code</x:v>
-      </x:c>
-      <x:c r="B6" s="162"/>
-      <x:c r="C6" s="162"/>
-      <x:c r="D6" s="162"/>
-      <x:c r="E6" s="162"/>
-      <x:c r="F6" s="162"/>
-      <x:c r="G6" s="162"/>
-      <x:c r="H6" s="162"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="168" t="str">
+      <x:c r="A6" s="249"/>
+      <x:c r="B6" s="249"/>
+      <x:c r="C6" s="249"/>
+      <x:c r="D6" s="249"/>
+      <x:c r="E6" s="249"/>
+      <x:c r="F6" s="249"/>
+      <x:c r="G6" s="249"/>
+      <x:c r="H6" s="249"/>
+    </x:row>
+    <x:row r="7" ht="32" customHeight="1">
+      <x:c r="A7" s="252" t="str">
         <x:v>Error Code</x:v>
       </x:c>
-      <x:c r="B7" s="168" t="str">
+      <x:c r="B7" s="252" t="str">
         <x:v>分類</x:v>
       </x:c>
-      <x:c r="C7" s="168" t="str">
-        <x:v>意味</x:v>
-      </x:c>
-      <x:c r="D7" s="168" t="str">
+      <x:c r="C7" s="252" t="str">
+        <x:v>業務上の意味</x:v>
+      </x:c>
+      <x:c r="D7" s="252" t="str">
         <x:v>HTTP Status</x:v>
       </x:c>
-      <x:c r="E7" s="168" t="str">
-        <x:v>画面Message</x:v>
-      </x:c>
-      <x:c r="F7" s="168" t="str">
-        <x:v>記録Level</x:v>
-      </x:c>
-      <x:c r="G7" s="168" t="str">
+      <x:c r="E7" s="252" t="str">
+        <x:v>Message参照</x:v>
+      </x:c>
+      <x:c r="F7" s="252" t="str">
+        <x:v>Log Level</x:v>
+      </x:c>
+      <x:c r="G7" s="252" t="str">
         <x:v>再試行</x:v>
       </x:c>
-      <x:c r="H7" s="168" t="str">
+      <x:c r="H7" s="252" t="str">
         <x:v>備考</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="67" t="str">
-        <x:v>COMMON-0000</x:v>
-      </x:c>
-      <x:c r="B8" s="67" t="str">
-        <x:v>成功</x:v>
-      </x:c>
-      <x:c r="C8" s="67" t="str">
-        <x:v>処理成功</x:v>
-      </x:c>
-      <x:c r="D8" s="67" t="n">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="E8" s="67" t="str">
-        <x:v>処理成功</x:v>
-      </x:c>
-      <x:c r="F8" s="67" t="str">
-        <x:v>INFO</x:v>
-      </x:c>
-      <x:c r="G8" s="67" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H8" s="67"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="67" t="str">
-        <x:v>COMMON-4000</x:v>
-      </x:c>
-      <x:c r="B9" s="67" t="str">
-        <x:v>入力</x:v>
-      </x:c>
-      <x:c r="C9" s="67" t="str">
-        <x:v>Request parameter error</x:v>
-      </x:c>
-      <x:c r="D9" s="67" t="n">
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="254" t="str">
+        <x:v>PRJ-4001</x:v>
+      </x:c>
+      <x:c r="B8" s="254" t="str">
+        <x:v>PJ</x:v>
+      </x:c>
+      <x:c r="C8" s="254" t="str">
+        <x:v>PJ番号重複</x:v>
+      </x:c>
+      <x:c r="D8" s="254" t="n">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="E8" s="254" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F8" s="254" t="str">
+        <x:v>WARN</x:v>
+      </x:c>
+      <x:c r="G8" s="254" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H8" s="254" t="str"/>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="253" t="str">
+        <x:v>PRJ-4002</x:v>
+      </x:c>
+      <x:c r="B9" s="253" t="str">
+        <x:v>PJ</x:v>
+      </x:c>
+      <x:c r="C9" s="253" t="str">
+        <x:v>日付不正</x:v>
+      </x:c>
+      <x:c r="D9" s="253" t="n">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="E9" s="67" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F9" s="67" t="str">
+      <x:c r="E9" s="253" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F9" s="253" t="str">
         <x:v>WARN</x:v>
       </x:c>
-      <x:c r="G9" s="67" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H9" s="67"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="67" t="str">
-        <x:v>COMMON-4040</x:v>
-      </x:c>
-      <x:c r="B10" s="67" t="str">
-        <x:v>Data</x:v>
-      </x:c>
-      <x:c r="C10" s="67" t="str">
-        <x:v>Data存在しない</x:v>
-      </x:c>
-      <x:c r="D10" s="67" t="n">
-        <x:v>404</x:v>
-      </x:c>
-      <x:c r="E10" s="67" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F10" s="67" t="str">
+      <x:c r="G9" s="253" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H9" s="253" t="str"/>
+    </x:row>
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="254" t="str">
+        <x:v>PRJ-4003</x:v>
+      </x:c>
+      <x:c r="B10" s="254" t="str">
+        <x:v>PJ</x:v>
+      </x:c>
+      <x:c r="C10" s="254" t="str">
+        <x:v>状態上操作不可</x:v>
+      </x:c>
+      <x:c r="D10" s="254" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="E10" s="254" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F10" s="254" t="str">
         <x:v>WARN</x:v>
       </x:c>
-      <x:c r="G10" s="67" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H10" s="67"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="67" t="str">
-        <x:v>COMMON-4090</x:v>
-      </x:c>
-      <x:c r="B11" s="67" t="str">
-        <x:v>競合</x:v>
-      </x:c>
-      <x:c r="C11" s="67" t="str">
-        <x:v>並行更新Conflict</x:v>
-      </x:c>
-      <x:c r="D11" s="67" t="n">
+      <x:c r="G10" s="254" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H10" s="254" t="str"/>
+    </x:row>
+    <x:row r="11" ht="42" customHeight="1">
+      <x:c r="A11" s="253" t="str">
+        <x:v>PRJ-4004</x:v>
+      </x:c>
+      <x:c r="B11" s="253" t="str">
+        <x:v>PJ</x:v>
+      </x:c>
+      <x:c r="C11" s="253" t="str">
+        <x:v>ACTIVE Member重複または同日再参加不可</x:v>
+      </x:c>
+      <x:c r="D11" s="253" t="n">
         <x:v>409</x:v>
       </x:c>
-      <x:c r="E11" s="67" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F11" s="67" t="str">
+      <x:c r="E11" s="253" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F11" s="253" t="str">
         <x:v>WARN</x:v>
       </x:c>
-      <x:c r="G11" s="67" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H11" s="67"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="67" t="str">
-        <x:v>COMMON-5000</x:v>
-      </x:c>
-      <x:c r="B12" s="67" t="str">
-        <x:v>System</x:v>
-      </x:c>
-      <x:c r="C12" s="67" t="str">
-        <x:v>System error</x:v>
-      </x:c>
-      <x:c r="D12" s="67" t="n">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="E12" s="67" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F12" s="67" t="str">
-        <x:v>ERROR</x:v>
-      </x:c>
-      <x:c r="G12" s="67" t="str">
-        <x:v>可</x:v>
-      </x:c>
-      <x:c r="H12" s="67"/>
+      <x:c r="G11" s="253" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H11" s="253" t="str"/>
+    </x:row>
+    <x:row r="12" ht="57" customHeight="1">
+      <x:c r="A12" s="254" t="str">
+        <x:v>PRJ-4005</x:v>
+      </x:c>
+      <x:c r="B12" s="254" t="str">
+        <x:v>PJ Member</x:v>
+      </x:c>
+      <x:c r="C12" s="254" t="str">
+        <x:v>PM、未完了Task担当者またはReview待ち担当者のため削除不可</x:v>
+      </x:c>
+      <x:c r="D12" s="254" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="E12" s="254" t="str">
+        <x:v>18／31B_ErrorMessage対応参照</x:v>
+      </x:c>
+      <x:c r="F12" s="254" t="str">
+        <x:v>WARN</x:v>
+      </x:c>
+      <x:c r="G12" s="254" t="str">
+        <x:v>不可</x:v>
+      </x:c>
+      <x:c r="H12" s="254" t="str">
+        <x:v>BR-MEM-002</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="67" t="str">
-        <x:v>PRJ-4001</x:v>
-      </x:c>
-      <x:c r="B13" s="67" t="str">
-        <x:v>PJ</x:v>
-      </x:c>
-      <x:c r="C13" s="67" t="str">
-        <x:v>PJ番号重複</x:v>
-      </x:c>
-      <x:c r="D13" s="67" t="n">
-        <x:v>409</x:v>
-      </x:c>
-      <x:c r="E13" s="67" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F13" s="67" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G13" s="67" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H13" s="67"/>
+      <x:c r="A13"/>
+      <x:c r="B13"/>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
+      <x:c r="E13"/>
+      <x:c r="F13"/>
+      <x:c r="G13"/>
+      <x:c r="H13"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="67" t="str">
-        <x:v>PRJ-4002</x:v>
-      </x:c>
-      <x:c r="B14" s="67" t="str">
-        <x:v>PJ</x:v>
-      </x:c>
-      <x:c r="C14" s="67" t="str">
-        <x:v>日付不正</x:v>
-      </x:c>
-      <x:c r="D14" s="67" t="n">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="E14" s="67" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F14" s="67" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G14" s="67" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H14" s="67"/>
+      <x:c r="A14"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="67" t="str">
-        <x:v>PRJ-4003</x:v>
-      </x:c>
-      <x:c r="B15" s="67" t="str">
-        <x:v>PJ</x:v>
-      </x:c>
-      <x:c r="C15" s="67" t="str">
-        <x:v>状態上操作不可</x:v>
-      </x:c>
-      <x:c r="D15" s="67" t="n">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="E15" s="67" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F15" s="67" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G15" s="67" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H15" s="67"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="67" t="str">
-        <x:v>PRJ-4004</x:v>
-      </x:c>
-      <x:c r="B16" s="67" t="str">
-        <x:v>PJ</x:v>
-      </x:c>
-      <x:c r="C16" s="67" t="str">
-        <x:v>Member重複</x:v>
-      </x:c>
-      <x:c r="D16" s="67" t="n">
-        <x:v>409</x:v>
-      </x:c>
-      <x:c r="E16" s="67" t="str">
-        <x:v>入力または処理内容を確認してください。</x:v>
-      </x:c>
-      <x:c r="F16" s="67" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G16" s="67" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H16" s="67"/>
+      <x:c r="A15"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
+      <x:c r="F15"/>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
+    </x:row>
+    <x:row r="16" ht="40" customHeight="1">
+      <x:c r="A16"/>
+      <x:c r="B16"/>
+      <x:c r="C16"/>
+      <x:c r="D16"/>
+      <x:c r="E16"/>
+      <x:c r="F16"/>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="67" t="str">
-        <x:v>PRJ-4005</x:v>
-      </x:c>
-      <x:c r="B17" s="67" t="str">
-        <x:v>PJ Member</x:v>
-      </x:c>
-      <x:c r="C17" s="67" t="str">
-        <x:v>PM、未完了Task担当者またはReview待ち担当者のため削除不可</x:v>
-      </x:c>
-      <x:c r="D17" s="67" t="n">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="E17" s="67" t="str">
-        <x:v>対象Memberの役割または担当Taskを確認してください。</x:v>
-      </x:c>
-      <x:c r="F17" s="67" t="str">
-        <x:v>WARN</x:v>
-      </x:c>
-      <x:c r="G17" s="67" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="H17" s="67" t="str">
-        <x:v>BR-MEM-002</x:v>
-      </x:c>
+      <x:c r="A17"/>
+      <x:c r="B17"/>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
+      <x:c r="E17"/>
+      <x:c r="F17"/>
+      <x:c r="G17"/>
+      <x:c r="H17"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18"/>
@@ -3075,16 +3169,9 @@
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:H2"/>
-    <x:mergeCell ref="A3:B3"/>
-    <x:mergeCell ref="C3:D3"/>
-    <x:mergeCell ref="E3:F3"/>
-    <x:mergeCell ref="G3:H3"/>
-    <x:mergeCell ref="A4:B4"/>
-    <x:mergeCell ref="C4:D4"/>
-    <x:mergeCell ref="E4:F4"/>
-    <x:mergeCell ref="G4:H4"/>
-    <x:mergeCell ref="A6:H6"/>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A3:H3"/>
+    <x:mergeCell ref="A5:H5"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -3095,19 +3182,19 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="72" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="72" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="48" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="34" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="90" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="48" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="34" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="44" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="30" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="30" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="68" t="str">
-        <x:v>API外部契約</x:v>
+        <x:v>API処理・権限概要</x:v>
       </x:c>
       <x:c r="B1" s="68"/>
       <x:c r="C1" s="68"/>
@@ -3115,8 +3202,6 @@
       <x:c r="E1" s="68"/>
       <x:c r="F1" s="68"/>
       <x:c r="G1" s="68"/>
-      <x:c r="H1" s="68"/>
-      <x:c r="I1" s="68"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="68"/>
@@ -3126,8 +3211,6 @@
       <x:c r="E2" s="68"/>
       <x:c r="F2" s="68"/>
       <x:c r="G2" s="68"/>
-      <x:c r="H2" s="68"/>
-      <x:c r="I2" s="68"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="62" t="str">
@@ -3137,35 +3220,31 @@
         <x:v>Company WorkHub</x:v>
       </x:c>
       <x:c r="C3" s="63"/>
-      <x:c r="D3" s="63"/>
-      <x:c r="E3" s="62" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="F3" s="63" t="str">
-        <x:v>CW-BD-API-PRJ-CONTRACT</x:v>
-      </x:c>
+      <x:c r="D3" s="246" t="str">
+        <x:v>章ID</x:v>
+      </x:c>
+      <x:c r="E3" s="63" t="str">
+        <x:v>CW-BD-API-PRJ-FLOW</x:v>
+      </x:c>
+      <x:c r="F3" s="63"/>
       <x:c r="G3" s="63"/>
-      <x:c r="H3" s="63"/>
-      <x:c r="I3" s="63"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="62" t="str">
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="63" t="str">
-        <x:v>Ver.1.8</x:v>
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="C4" s="63"/>
-      <x:c r="D4" s="63"/>
-      <x:c r="E4" s="62" t="str">
+      <x:c r="D4" s="62" t="str">
         <x:v>改訂日</x:v>
       </x:c>
-      <x:c r="F4" s="63" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
+      <x:c r="E4" s="63" t="str">
+        <x:v>2026-09-24</x:v>
+      </x:c>
+      <x:c r="F4" s="63"/>
       <x:c r="G4" s="63"/>
-      <x:c r="H4" s="63"/>
-      <x:c r="I4" s="63"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="64"/>
@@ -3175,12 +3254,10 @@
       <x:c r="E5" s="64"/>
       <x:c r="F5" s="64"/>
       <x:c r="G5" s="64"/>
-      <x:c r="H5" s="64"/>
-      <x:c r="I5" s="64"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="65" t="str">
-        <x:v>1. Project Request/Response・権限契約</x:v>
+        <x:v>1. API単位処理概要</x:v>
       </x:c>
       <x:c r="B6" s="65"/>
       <x:c r="C6" s="65"/>
@@ -3188,36 +3265,34 @@
       <x:c r="E6" s="65"/>
       <x:c r="F6" s="65"/>
       <x:c r="G6" s="65"/>
-      <x:c r="H6" s="65"/>
-      <x:c r="I6" s="65"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="66" t="str">
         <x:v>API ID</x:v>
       </x:c>
       <x:c r="B7" s="66" t="str">
-        <x:v>Request定義</x:v>
+        <x:v>機能</x:v>
       </x:c>
       <x:c r="C7" s="66" t="str">
-        <x:v>Response定義</x:v>
-      </x:c>
-      <x:c r="D7" s="66" t="str">
-        <x:v>Role</x:v>
+        <x:v>処理概要</x:v>
+      </x:c>
+      <x:c r="D7" s="255" t="str">
+        <x:v>認可参照</x:v>
       </x:c>
       <x:c r="E7" s="66" t="str">
-        <x:v>Data範囲</x:v>
+        <x:v>Transaction</x:v>
       </x:c>
       <x:c r="F7" s="66" t="str">
-        <x:v>参照・更新Table</x:v>
+        <x:v>Error Code</x:v>
       </x:c>
       <x:c r="G7" s="66" t="str">
-        <x:v>Transaction</x:v>
-      </x:c>
-      <x:c r="H7" s="66" t="str">
-        <x:v>Error Code</x:v>
-      </x:c>
-      <x:c r="I7" s="66" t="str">
-        <x:v>利用画面</x:v>
+        <x:v>Log</x:v>
+      </x:c>
+      <x:c r="H7" s="203" t="str">
+        <x:v>関連Table</x:v>
+      </x:c>
+      <x:c r="I7" s="203" t="str">
+        <x:v>利用元・補足</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
@@ -3225,27 +3300,29 @@
         <x:v>API-PRJ-001</x:v>
       </x:c>
       <x:c r="B8" s="67" t="str">
-        <x:v>query: code,name,managerId,status,startFrom,startTo,endFrom,endTo,mine,page,size,sort</x:v>
+        <x:v>PJ検索</x:v>
       </x:c>
       <x:c r="C8" s="67" t="str">
-        <x:v>Page&lt;ProjectSummary&gt;</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) projects,project_members,employees,tasksを参照。4) 業務Dataの更新なし。5) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D8" s="67" t="str">
-        <x:v>全員</x:v>
+        <x:v>02／13_API権限対応 API-PRJ-001
+Permission: PERM-PRJ-READ
+Data Scope: DS-PRJ-001</x:v>
       </x:c>
       <x:c r="E8" s="67" t="str">
-        <x:v>ADMIN=全社, PM/EMP=担当・参加PJ</x:v>
+        <x:v>参照</x:v>
       </x:c>
       <x:c r="F8" s="67" t="str">
+        <x:v>COMMON-4000</x:v>
+      </x:c>
+      <x:c r="G8" s="67" t="str">
+        <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
+      </x:c>
+      <x:c r="H8" s="203" t="str">
         <x:v>projects,project_members,employees,tasks</x:v>
       </x:c>
-      <x:c r="G8" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="H8" s="67" t="str">
-        <x:v>COMMON-4000</x:v>
-      </x:c>
-      <x:c r="I8" s="67" t="str">
+      <x:c r="I8" s="203" t="str">
         <x:v>SCR-008</x:v>
       </x:c>
     </x:row>
@@ -3254,540 +3331,235 @@
         <x:v>API-PRJ-002</x:v>
       </x:c>
       <x:c r="B9" s="67" t="str">
-        <x:v>path: id Long</x:v>
+        <x:v>PJ詳細</x:v>
       </x:c>
       <x:c r="C9" s="67" t="str">
-        <x:v>ProjectDetail + members[] + taskSummary</x:v>
+        <x:v>1) 02の対応Permission/Data Scopeを判定。2) 23_API項目定義に従い入力を検証。3) projects,project_members,employees,tasksを参照。4) 業務Dataの更新なし。5) 23_API項目定義の正常Responseを返す。</x:v>
       </x:c>
       <x:c r="D9" s="67" t="str">
-        <x:v>関係者</x:v>
+        <x:v>02／13_API権限対応 API-PRJ-002
+Permission: PERM-PRJ-READ
+Data Scope: DS-PRJ-002</x:v>
       </x:c>
       <x:c r="E9" s="67" t="str">
-        <x:v>ADMINまたはPJ Member</x:v>
+        <x:v>参照</x:v>
       </x:c>
       <x:c r="F9" s="67" t="str">
+        <x:v>COMMON-4040/AUTH-4006</x:v>
+      </x:c>
+      <x:c r="G9" s="67" t="str">
+        <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
+      </x:c>
+      <x:c r="H9" s="203" t="str">
         <x:v>projects,project_members,employees,tasks</x:v>
       </x:c>
-      <x:c r="G9" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="H9" s="67" t="str">
-        <x:v>COMMON-4040/AUTH-4006</x:v>
-      </x:c>
-      <x:c r="I9" s="67" t="str">
+      <x:c r="I9" s="203" t="str">
         <x:v>SCR-010, SCR-011</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="30" customHeight="1">
+    <x:row r="10" ht="96" customHeight="1">
       <x:c r="A10" s="67" t="str">
         <x:v>API-PRJ-003</x:v>
       </x:c>
       <x:c r="B10" s="67" t="str">
-        <x:v>body: projectCode,name,managerId,startDate,endDate,status,customerName,budgetHours,description; header: X-Idempotency-Key</x:v>
+        <x:v>PJ登録</x:v>
       </x:c>
       <x:c r="C10" s="67" t="str">
-        <x:v>id,projectCode,version</x:v>
+        <x:v>ADMIN・入力確認。status=PLANNINGのみ。日付順序、PM資格（16／28 BR-MEM-003）を確認。TX-002でPJと操作日からのACTIVE/PM Member、監査を登録。成功時id/projectCode/version。失敗全Rollback。</x:v>
       </x:c>
       <x:c r="D10" s="67" t="str">
-        <x:v>管理者</x:v>
+        <x:v>02／13_API権限対応 API-PRJ-003
+Permission: PERM-PRJ-WRITE
+Data Scope: DS-PRJ-003</x:v>
       </x:c>
       <x:c r="E10" s="67" t="str">
-        <x:v>管理者のみ</x:v>
+        <x:v>TX-002</x:v>
       </x:c>
       <x:c r="F10" s="67" t="str">
+        <x:v>COMMON-4000, PRJ-4001, PRJ-4002, COMMON-4090</x:v>
+      </x:c>
+      <x:c r="G10" s="67" t="str">
+        <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
+      </x:c>
+      <x:c r="H10" s="241" t="str">
         <x:v>projects,project_members,operation_logs</x:v>
       </x:c>
-      <x:c r="G10" s="67" t="str">
-        <x:v>TX-002</x:v>
-      </x:c>
-      <x:c r="H10" s="67" t="str">
-        <x:v>PRJ-4001, PRJ-4002,COMMON-4090</x:v>
-      </x:c>
-      <x:c r="I10" s="67" t="str">
+      <x:c r="I10" s="241" t="str">
         <x:v>SCR-009</x:v>
       </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
+      <x:c r="J10" s="241"/>
+      <x:c r="K10" s="241"/>
+      <x:c r="L10" s="241"/>
+    </x:row>
+    <x:row r="11" ht="110" customHeight="1">
       <x:c r="A11" s="67" t="str">
         <x:v>API-PRJ-004</x:v>
       </x:c>
       <x:c r="B11" s="67" t="str">
-        <x:v>path: id; body: name,managerId,startDate,endDate,customerName,budgetHours,description,version</x:v>
+        <x:v>PJ更新</x:v>
       </x:c>
       <x:c r="C11" s="67" t="str">
-        <x:v>id,version</x:v>
+        <x:v>ADMINまたは現PM・version確認。終端PJはPRJ-4003。新期間内に未削除Task/日報が収まることを確認（BR-PRJ-005）。PM変更はBR-MEM-003で資格/参加履歴確認し旧PMをMEMBER、新PMをPMへ。TX-003でPJ/Member/監査を一括更新。失敗全Rollback。</x:v>
       </x:c>
       <x:c r="D11" s="67" t="str">
-        <x:v>管理者/担当PM</x:v>
+        <x:v>02／13_API権限対応 API-PRJ-004
+Permission: PERM-PRJ-WRITE
+Data Scope: DS-PRJ-004</x:v>
       </x:c>
       <x:c r="E11" s="67" t="str">
-        <x:v>ADMINまたは当該PJのPM</x:v>
+        <x:v>TX-003</x:v>
       </x:c>
       <x:c r="F11" s="67" t="str">
+        <x:v>COMMON-4000, PRJ-4002, PRJ-4003, PRJ-4004, COMMON-4040, COMMON-4090</x:v>
+      </x:c>
+      <x:c r="G11" s="67" t="str">
+        <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
+      </x:c>
+      <x:c r="H11" s="241" t="str">
         <x:v>projects,project_members,operation_logs</x:v>
       </x:c>
-      <x:c r="G11" s="67" t="str">
-        <x:v>TX-003</x:v>
-      </x:c>
-      <x:c r="H11" s="67" t="str">
-        <x:v>PRJ-4001, PRJ-4002,COMMON-4040, COMMON-4090</x:v>
-      </x:c>
-      <x:c r="I11" s="67" t="str">
+      <x:c r="I11" s="241" t="str">
         <x:v>SCR-010</x:v>
       </x:c>
-    </x:row>
-    <x:row r="12" ht="30" customHeight="1">
+      <x:c r="J11" s="241"/>
+      <x:c r="K11" s="241"/>
+      <x:c r="L11" s="241"/>
+    </x:row>
+    <x:row r="12" ht="110" customHeight="1">
       <x:c r="A12" s="67" t="str">
         <x:v>API-PRJ-005</x:v>
       </x:c>
       <x:c r="B12" s="67" t="str">
-        <x:v>path: id; body: status,version</x:v>
+        <x:v>PJ状態変更</x:v>
       </x:c>
       <x:c r="C12" s="67" t="str">
-        <x:v>id,status,progress,version</x:v>
+        <x:v>ADMINまたは現PM・存在/versionを確認。16／27のPJ遷移だけを許可。同状態/終端再開は禁止。完了/取消は未削除TODO/IN_PROGRESS/REVIEWのTask0件を再確認。TX-018で状態/versionと監査をCommit。Task/Memberを自動更新しない。失敗全Rollback。</x:v>
       </x:c>
       <x:c r="D12" s="67" t="str">
-        <x:v>管理者/担当PM</x:v>
+        <x:v>02／13_API権限対応 API-PRJ-005
+Permission: PERM-PRJ-WRITE
+Data Scope: DS-PRJ-005</x:v>
       </x:c>
       <x:c r="E12" s="67" t="str">
-        <x:v>完了時に未完了Taskなし</x:v>
+        <x:v>TX-018</x:v>
       </x:c>
       <x:c r="F12" s="67" t="str">
+        <x:v>PRJ-4003, COMMON-4040, COMMON-4090</x:v>
+      </x:c>
+      <x:c r="G12" s="67" t="str">
+        <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
+      </x:c>
+      <x:c r="H12" s="241" t="str">
         <x:v>projects,tasks,operation_logs</x:v>
       </x:c>
-      <x:c r="G12" s="67" t="str">
-        <x:v>TX-018</x:v>
-      </x:c>
-      <x:c r="H12" s="67" t="str">
-        <x:v>PRJ-4003,COMMON-4090</x:v>
-      </x:c>
-      <x:c r="I12" s="67" t="str">
+      <x:c r="I12" s="241" t="str">
         <x:v>SCR-010, SCR-011</x:v>
       </x:c>
-    </x:row>
-    <x:row r="13" ht="30" customHeight="1">
+      <x:c r="J12" s="241"/>
+      <x:c r="K12" s="241"/>
+      <x:c r="L12" s="241"/>
+    </x:row>
+    <x:row r="13" ht="96" customHeight="1">
       <x:c r="A13" s="67" t="str">
         <x:v>API-PRJ-006</x:v>
       </x:c>
       <x:c r="B13" s="67" t="str">
-        <x:v>path: id; query: status,page,size</x:v>
+        <x:v>Member検索</x:v>
       </x:c>
       <x:c r="C13" s="67" t="str">
-        <x:v>Page&lt;ProjectMember&gt;</x:v>
+        <x:v>権限確認後、status省略はACTIVE、指定ACTIVE/LEFTで参加履歴行を取得。社員番号昇順、joined_date降順、id降順。LEFT履歴は同一社員複数行可。leftDate/versionを含む23項目契約のPageを返す。0件は空Page。</x:v>
       </x:c>
       <x:c r="D13" s="67" t="str">
-        <x:v>関係者</x:v>
+        <x:v>02／13_API権限対応 API-PRJ-006
+Permission: PERM-PRJ-READ
+Data Scope: DS-PRJ-006</x:v>
       </x:c>
       <x:c r="E13" s="67" t="str">
-        <x:v>ADMINまたはPJ Member</x:v>
+        <x:v>参照</x:v>
       </x:c>
       <x:c r="F13" s="67" t="str">
+        <x:v>AUTH-4006</x:v>
+      </x:c>
+      <x:c r="G13" s="67" t="str">
+        <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
+      </x:c>
+      <x:c r="H13" s="241" t="str">
         <x:v>project_members,employees,departments</x:v>
       </x:c>
-      <x:c r="G13" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="H13" s="67" t="str">
-        <x:v>AUTH-4006</x:v>
-      </x:c>
-      <x:c r="I13" s="67" t="str">
+      <x:c r="I13" s="241" t="str">
         <x:v>SCR-011, SCR-012</x:v>
       </x:c>
-    </x:row>
-    <x:row r="14" ht="30" customHeight="1">
+      <x:c r="J13" s="241"/>
+      <x:c r="K13" s="241"/>
+      <x:c r="L13" s="241"/>
+    </x:row>
+    <x:row r="14" ht="124" customHeight="1">
       <x:c r="A14" s="67" t="str">
         <x:v>API-PRJ-007</x:v>
       </x:c>
       <x:c r="B14" s="67" t="str">
-        <x:v>path: id; body: employeeId,projectRole,joinedDate; header: X-Idempotency-Key</x:v>
+        <x:v>Member追加</x:v>
       </x:c>
       <x:c r="C14" s="67" t="str">
-        <x:v>id,employeeId,version</x:v>
+        <x:v>ADMINまたは現PM、PJ非終端、在籍有効社員、projectRole=MEMBER、joinedDate=当日を確認。ACTIVE重複または最新left_date≧当日はPRJ-4004。TX-019でPJ/社員を排他し新ACTIVE行を追加。LEFT行再有効化なし。成功時新Member ID/employeeId/version。</x:v>
       </x:c>
       <x:c r="D14" s="67" t="str">
-        <x:v>管理者/担当PM</x:v>
+        <x:v>02／13_API権限対応 API-PRJ-007
+Permission: PERM-MEMBER-WRITE
+Data Scope: DS-PRJ-007</x:v>
       </x:c>
       <x:c r="E14" s="67" t="str">
-        <x:v>ADMINまたは当該PJのPM; 在籍社員</x:v>
+        <x:v>TX-019</x:v>
       </x:c>
       <x:c r="F14" s="67" t="str">
+        <x:v>COMMON-4000, PRJ-4003, PRJ-4004, COMMON-4090</x:v>
+      </x:c>
+      <x:c r="G14" s="67" t="str">
+        <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
+      </x:c>
+      <x:c r="H14" s="241" t="str">
         <x:v>project_members,employees,projects,operation_logs</x:v>
       </x:c>
-      <x:c r="G14" s="67" t="str">
-        <x:v>TX-019</x:v>
-      </x:c>
-      <x:c r="H14" s="67" t="str">
-        <x:v>PRJ-4004,COMMON-4090</x:v>
-      </x:c>
-      <x:c r="I14" s="67" t="str">
+      <x:c r="I14" s="241" t="str">
         <x:v>SCR-012</x:v>
       </x:c>
-    </x:row>
-    <x:row r="15" ht="30" customHeight="1">
+      <x:c r="J14" s="241"/>
+      <x:c r="K14" s="241"/>
+      <x:c r="L14" s="241"/>
+    </x:row>
+    <x:row r="15" ht="110" customHeight="1">
       <x:c r="A15" s="67" t="str">
         <x:v>API-PRJ-008</x:v>
       </x:c>
       <x:c r="B15" s="67" t="str">
-        <x:v>path: id,employeeId; query: version</x:v>
+        <x:v>Member削除</x:v>
       </x:c>
       <x:c r="C15" s="67" t="str">
-        <x:v>204 No Content</x:v>
+        <x:v>ADMINまたは現PM、非終端PJを確認。path社員のACTIVE行を特定（なければ404）、その行のversion照合。PM/未完了Task担当者はPRJ-4005。TX-019でLEFT、left_date=当日、version+1、監査を更新。既存履歴/日報は保持。204本文なし。</x:v>
       </x:c>
       <x:c r="D15" s="67" t="str">
-        <x:v>管理者/担当PM</x:v>
-      </x:c>
-      <x:c r="E15" s="67" t="str">
-        <x:v>PM・未完了Task担当者は削除不可</x:v>
-      </x:c>
-      <x:c r="F15" s="67" t="str">
-        <x:v>project_members,tasks,operation_logs</x:v>
-      </x:c>
-      <x:c r="G15" s="67" t="str">
-        <x:v>TX-019</x:v>
-      </x:c>
-      <x:c r="H15" s="67" t="str">
-        <x:v>PRJ-4005,COMMON-4090</x:v>
-      </x:c>
-      <x:c r="I15" s="67" t="str">
-        <x:v>SCR-012</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="64"/>
-      <x:c r="B16" s="64"/>
-      <x:c r="C16" s="64"/>
-      <x:c r="D16" s="64"/>
-      <x:c r="E16" s="64"/>
-      <x:c r="F16" s="64"/>
-      <x:c r="G16" s="64"/>
-      <x:c r="H16" s="64"/>
-      <x:c r="I16" s="64"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17"/>
-      <x:c r="B17"/>
-      <x:c r="C17"/>
-      <x:c r="D17"/>
-      <x:c r="E17"/>
-      <x:c r="F17"/>
-      <x:c r="G17"/>
-      <x:c r="H17"/>
-      <x:c r="I17"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="91"/>
-      <x:c r="B18" s="92"/>
-      <x:c r="C18" s="92"/>
-      <x:c r="D18" s="92"/>
-      <x:c r="E18" s="92"/>
-      <x:c r="F18" s="92"/>
-      <x:c r="G18" s="92"/>
-      <x:c r="H18" s="92"/>
-      <x:c r="I18" s="93"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:I2"/>
-    <x:mergeCell ref="A6:I6"/>
-    <x:mergeCell ref="A17:I18"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="90" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="48" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="34" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="44" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="68" t="str">
-        <x:v>API処理・権限概要</x:v>
-      </x:c>
-      <x:c r="B1" s="68"/>
-      <x:c r="C1" s="68"/>
-      <x:c r="D1" s="68"/>
-      <x:c r="E1" s="68"/>
-      <x:c r="F1" s="68"/>
-      <x:c r="G1" s="68"/>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="68"/>
-      <x:c r="B2" s="68"/>
-      <x:c r="C2" s="68"/>
-      <x:c r="D2" s="68"/>
-      <x:c r="E2" s="68"/>
-      <x:c r="F2" s="68"/>
-      <x:c r="G2" s="68"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="62" t="str">
-        <x:v>システム名</x:v>
-      </x:c>
-      <x:c r="B3" s="63" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="C3" s="63"/>
-      <x:c r="D3" s="62" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="E3" s="63" t="str">
-        <x:v>CW-BD-API-PRJ-FLOW</x:v>
-      </x:c>
-      <x:c r="F3" s="63"/>
-      <x:c r="G3" s="63"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="62" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="63" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="C4" s="63"/>
-      <x:c r="D4" s="62" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
-      <x:c r="E4" s="63" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
-      <x:c r="F4" s="63"/>
-      <x:c r="G4" s="63"/>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="64"/>
-      <x:c r="B5" s="64"/>
-      <x:c r="C5" s="64"/>
-      <x:c r="D5" s="64"/>
-      <x:c r="E5" s="64"/>
-      <x:c r="F5" s="64"/>
-      <x:c r="G5" s="64"/>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="65" t="str">
-        <x:v>1. API単位処理概要</x:v>
-      </x:c>
-      <x:c r="B6" s="65"/>
-      <x:c r="C6" s="65"/>
-      <x:c r="D6" s="65"/>
-      <x:c r="E6" s="65"/>
-      <x:c r="F6" s="65"/>
-      <x:c r="G6" s="65"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="66" t="str">
-        <x:v>API ID</x:v>
-      </x:c>
-      <x:c r="B7" s="66" t="str">
-        <x:v>機能</x:v>
-      </x:c>
-      <x:c r="C7" s="66" t="str">
-        <x:v>処理概要</x:v>
-      </x:c>
-      <x:c r="D7" s="66" t="str">
-        <x:v>Data範囲</x:v>
-      </x:c>
-      <x:c r="E7" s="66" t="str">
-        <x:v>Transaction</x:v>
-      </x:c>
-      <x:c r="F7" s="66" t="str">
-        <x:v>Error Code</x:v>
-      </x:c>
-      <x:c r="G7" s="66" t="str">
-        <x:v>Log</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="67" t="str">
-        <x:v>API-PRJ-001</x:v>
-      </x:c>
-      <x:c r="B8" s="67" t="str">
-        <x:v>PJ検索</x:v>
-      </x:c>
-      <x:c r="C8" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) query: code,name,managerId,status,startFrom,startTo,endFrom,endTo,mine,page,size,sortを型・必須・桁・業務Ruleで検証。3) projects,project_members,employees,tasksを参照/更新。4) 参照の境界でCommit/Rollback。5) Page&lt;ProjectSummary&gt;を共通Response形式で返却。</x:v>
-      </x:c>
-      <x:c r="D8" s="67" t="str">
-        <x:v>ADMIN=全社, PM/EMP=担当・参加PJ</x:v>
-      </x:c>
-      <x:c r="E8" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="F8" s="67" t="str">
-        <x:v>COMMON-4000</x:v>
-      </x:c>
-      <x:c r="G8" s="67" t="str">
-        <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="67" t="str">
-        <x:v>API-PRJ-002</x:v>
-      </x:c>
-      <x:c r="B9" s="67" t="str">
-        <x:v>PJ詳細</x:v>
-      </x:c>
-      <x:c r="C9" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) path: id Longを型・必須・桁・業務Ruleで検証。3) projects,project_members,employees,tasksを参照/更新。4) 参照の境界でCommit/Rollback。5) ProjectDetail + members[] + taskSummaryを共通Response形式で返却。</x:v>
-      </x:c>
-      <x:c r="D9" s="67" t="str">
-        <x:v>ADMINまたはPJ Member</x:v>
-      </x:c>
-      <x:c r="E9" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="F9" s="67" t="str">
-        <x:v>COMMON-4040/AUTH-4006</x:v>
-      </x:c>
-      <x:c r="G9" s="67" t="str">
-        <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="67" t="str">
-        <x:v>API-PRJ-003</x:v>
-      </x:c>
-      <x:c r="B10" s="67" t="str">
-        <x:v>PJ登録</x:v>
-      </x:c>
-      <x:c r="C10" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) body: projectCode,name,managerId,startDate,endDate,status,customerName,budgetHours,description; header: X-Idempotency-Keyを型・必須・桁・業務Ruleで検証。3) projects,project_members,operation_logsを参照/更新。4) TX-002の境界でCommit/Rollback。5) id,projectCode,versionを共通Response形式で返却。</x:v>
-      </x:c>
-      <x:c r="D10" s="67" t="str">
-        <x:v>管理者のみ</x:v>
-      </x:c>
-      <x:c r="E10" s="67" t="str">
-        <x:v>TX-002</x:v>
-      </x:c>
-      <x:c r="F10" s="67" t="str">
-        <x:v>PRJ-4001, PRJ-4002,COMMON-4090</x:v>
-      </x:c>
-      <x:c r="G10" s="67" t="str">
-        <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="67" t="str">
-        <x:v>API-PRJ-004</x:v>
-      </x:c>
-      <x:c r="B11" s="67" t="str">
-        <x:v>PJ更新</x:v>
-      </x:c>
-      <x:c r="C11" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) path: id; body: name,managerId,startDate,endDate,customerName,budgetHours,description,versionを型・必須・桁・業務Ruleで検証。3) projects,project_members,operation_logsを参照/更新。4) TX-003の境界でCommit/Rollback。5) id,versionを共通Response形式で返却。</x:v>
-      </x:c>
-      <x:c r="D11" s="67" t="str">
-        <x:v>ADMINまたは当該PJのPM</x:v>
-      </x:c>
-      <x:c r="E11" s="67" t="str">
-        <x:v>TX-003</x:v>
-      </x:c>
-      <x:c r="F11" s="67" t="str">
-        <x:v>PRJ-4001, PRJ-4002,COMMON-4040, COMMON-4090</x:v>
-      </x:c>
-      <x:c r="G11" s="67" t="str">
-        <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="30" customHeight="1">
-      <x:c r="A12" s="67" t="str">
-        <x:v>API-PRJ-005</x:v>
-      </x:c>
-      <x:c r="B12" s="67" t="str">
-        <x:v>PJ状態変更</x:v>
-      </x:c>
-      <x:c r="C12" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) path: id; body: status,versionを型・必須・桁・業務Ruleで検証。3) projects,tasks,operation_logsを参照/更新。4) TX-PRJ-STATUSの境界でCommit/Rollback。5) id,status,progress,versionを共通Response形式で返却。</x:v>
-      </x:c>
-      <x:c r="D12" s="67" t="str">
-        <x:v>完了時に未完了Taskなし</x:v>
-      </x:c>
-      <x:c r="E12" s="67" t="str">
-        <x:v>TX-018</x:v>
-      </x:c>
-      <x:c r="F12" s="67" t="str">
-        <x:v>PRJ-4003,COMMON-4090</x:v>
-      </x:c>
-      <x:c r="G12" s="67" t="str">
-        <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="30" customHeight="1">
-      <x:c r="A13" s="67" t="str">
-        <x:v>API-PRJ-006</x:v>
-      </x:c>
-      <x:c r="B13" s="67" t="str">
-        <x:v>Member検索</x:v>
-      </x:c>
-      <x:c r="C13" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) path: id; query: status,page,sizeを型・必須・桁・業務Ruleで検証。3) project_members,employees,departmentsを参照/更新。4) 参照の境界でCommit/Rollback。5) Page&lt;ProjectMember&gt;を共通Response形式で返却。</x:v>
-      </x:c>
-      <x:c r="D13" s="67" t="str">
-        <x:v>ADMINまたはPJ Member</x:v>
-      </x:c>
-      <x:c r="E13" s="67" t="str">
-        <x:v>参照</x:v>
-      </x:c>
-      <x:c r="F13" s="67" t="str">
-        <x:v>AUTH-4006</x:v>
-      </x:c>
-      <x:c r="G13" s="67" t="str">
-        <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="30" customHeight="1">
-      <x:c r="A14" s="67" t="str">
-        <x:v>API-PRJ-007</x:v>
-      </x:c>
-      <x:c r="B14" s="67" t="str">
-        <x:v>Member追加</x:v>
-      </x:c>
-      <x:c r="C14" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) path: id; body: employeeId,projectRole,joinedDate; header: X-Idempotency-Keyを型・必須・桁・業務Ruleで検証。3) project_members,employees,projects,operation_logsを参照/更新。4) TX-PRJ-MEMBERの境界でCommit/Rollback。5) id,employeeId,versionを共通Response形式で返却。</x:v>
-      </x:c>
-      <x:c r="D14" s="67" t="str">
-        <x:v>ADMINまたは当該PJのPM; 在籍社員</x:v>
-      </x:c>
-      <x:c r="E14" s="67" t="str">
-        <x:v>TX-019</x:v>
-      </x:c>
-      <x:c r="F14" s="67" t="str">
-        <x:v>PRJ-4004,COMMON-4090</x:v>
-      </x:c>
-      <x:c r="G14" s="67" t="str">
-        <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="30" customHeight="1">
-      <x:c r="A15" s="67" t="str">
-        <x:v>API-PRJ-008</x:v>
-      </x:c>
-      <x:c r="B15" s="67" t="str">
-        <x:v>Member削除</x:v>
-      </x:c>
-      <x:c r="C15" s="67" t="str">
-        <x:v>1) 認証・権限・Data範囲を確認。2) path: id,employeeId; query: versionを型・必須・桁・業務Ruleで検証。3) project_members,tasks,operation_logsを参照/更新。4) TX-PRJ-MEMBERの境界でCommit/Rollback。5) 204 No Contentを共通Response形式で返却。</x:v>
-      </x:c>
-      <x:c r="D15" s="67" t="str">
-        <x:v>PM・未完了Task担当者は削除不可</x:v>
+        <x:v>02／13_API権限対応 API-PRJ-008
+Permission: PERM-MEMBER-WRITE
+Data Scope: DS-PRJ-008</x:v>
       </x:c>
       <x:c r="E15" s="67" t="str">
         <x:v>TX-019</x:v>
       </x:c>
       <x:c r="F15" s="67" t="str">
-        <x:v>PRJ-4005,COMMON-4090</x:v>
+        <x:v>PRJ-4003, PRJ-4005, COMMON-4040, COMMON-4090</x:v>
       </x:c>
       <x:c r="G15" s="67" t="str">
         <x:v>traceId付きLog。Password/Token/個人情報はMask</x:v>
       </x:c>
+      <x:c r="H15" s="241" t="str">
+        <x:v>project_members,tasks,operation_logs</x:v>
+      </x:c>
+      <x:c r="I15" s="241" t="str">
+        <x:v>SCR-012</x:v>
+      </x:c>
+      <x:c r="J15" s="241"/>
+      <x:c r="K15" s="241"/>
+      <x:c r="L15" s="241"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3798,7 +3570,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -3853,8 +3625,8 @@
       <x:c r="C3" s="139"/>
       <x:c r="D3" s="139"/>
       <x:c r="E3" s="139"/>
-      <x:c r="F3" s="174" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="F3" s="246" t="str">
+        <x:v>章ID</x:v>
       </x:c>
       <x:c r="G3" s="139" t="str">
         <x:v>CW-BD-12-FIELD</x:v>
@@ -3868,8 +3640,8 @@
       <x:c r="A4" s="174" t="str">
         <x:v>版数</x:v>
       </x:c>
-      <x:c r="B4" s="139" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="B4" s="63" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="C4" s="139"/>
       <x:c r="D4" s="139"/>
@@ -3877,8 +3649,8 @@
       <x:c r="F4" s="174" t="str">
         <x:v>改訂日</x:v>
       </x:c>
-      <x:c r="G4" s="139" t="str">
-        <x:v>2026-08-12</x:v>
+      <x:c r="G4" s="63" t="str">
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="H4" s="139"/>
       <x:c r="I4" s="139"/>
@@ -3990,7 +3762,7 @@
         <x:v>任意</x:v>
       </x:c>
       <x:c r="G9" s="67" t="str">
-        <x:v>最大100</x:v>
+        <x:v>最大200</x:v>
       </x:c>
       <x:c r="H9" s="67" t="str">
         <x:v>-</x:v>
@@ -4655,7 +4427,7 @@
         <x:v>必須</x:v>
       </x:c>
       <x:c r="G28" s="67" t="str">
-        <x:v>最大100</x:v>
+        <x:v>最大200</x:v>
       </x:c>
       <x:c r="H28" s="67" t="str">
         <x:v>-</x:v>
@@ -5495,7 +5267,7 @@
         <x:v>必須</x:v>
       </x:c>
       <x:c r="G52" s="67" t="str">
-        <x:v>最大100</x:v>
+        <x:v>最大200</x:v>
       </x:c>
       <x:c r="H52" s="67" t="str">
         <x:v>-</x:v>
@@ -6580,7 +6352,7 @@
         <x:v>必須</x:v>
       </x:c>
       <x:c r="G83" s="67" t="str">
-        <x:v>最大100</x:v>
+        <x:v>最大200</x:v>
       </x:c>
       <x:c r="H83" s="67" t="str">
         <x:v>-</x:v>
@@ -6700,7 +6472,7 @@
         <x:v>projects.end_date</x:v>
       </x:c>
     </x:row>
-    <x:row r="87" ht="24" hidden="0" customHeight="1">
+    <x:row r="87" ht="36" hidden="0" customHeight="1">
       <x:c r="A87" s="67" t="str">
         <x:v>API-PRJ-003</x:v>
       </x:c>
@@ -6723,17 +6495,18 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="H87" s="67" t="str">
-        <x:v>PLANNING/IN_PROGRESS/SUSPENDED/COMPLETED/CANCELLED</x:v>
+        <x:v>PLANNINGのみ</x:v>
       </x:c>
       <x:c r="I87" s="67" t="str">
         <x:v>不可</x:v>
       </x:c>
       <x:c r="J87" s="67" t="str">
-        <x:v>状態</x:v>
+        <x:v>初期状態固定。別値はCOMMON-4000。</x:v>
       </x:c>
       <x:c r="K87" s="67" t="str">
         <x:v>projects.status</x:v>
       </x:c>
+      <x:c r="L87" s="241"/>
     </x:row>
     <x:row r="88" ht="15" hidden="0" customHeight="1">
       <x:c r="A88" s="67" t="str">
@@ -6752,7 +6525,7 @@
         <x:v>String</x:v>
       </x:c>
       <x:c r="F88" s="67" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="G88" s="67" t="str">
         <x:v>最大200</x:v>
@@ -6761,7 +6534,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="I88" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J88" s="67" t="str">
         <x:v>顧客名</x:v>
@@ -6787,7 +6560,7 @@
         <x:v>Decimal</x:v>
       </x:c>
       <x:c r="F89" s="67" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="G89" s="67" t="str">
         <x:v>-</x:v>
@@ -6796,7 +6569,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="I89" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J89" s="67" t="str">
         <x:v>予算工数</x:v>
@@ -6822,7 +6595,7 @@
         <x:v>String</x:v>
       </x:c>
       <x:c r="F90" s="67" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="G90" s="67" t="str">
         <x:v>最大2000</x:v>
@@ -6831,7 +6604,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="I90" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J90" s="67" t="str">
         <x:v>説明</x:v>
@@ -7210,7 +6983,7 @@
         <x:v>必須</x:v>
       </x:c>
       <x:c r="G101" s="67" t="str">
-        <x:v>最大100</x:v>
+        <x:v>最大200</x:v>
       </x:c>
       <x:c r="H101" s="67" t="str">
         <x:v>-</x:v>
@@ -7347,7 +7120,7 @@
         <x:v>String</x:v>
       </x:c>
       <x:c r="F105" s="67" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="G105" s="67" t="str">
         <x:v>最大200</x:v>
@@ -7356,7 +7129,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="I105" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J105" s="67" t="str">
         <x:v>顧客名</x:v>
@@ -7382,7 +7155,7 @@
         <x:v>Decimal</x:v>
       </x:c>
       <x:c r="F106" s="67" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="G106" s="67" t="str">
         <x:v>-</x:v>
@@ -7391,7 +7164,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="I106" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J106" s="67" t="str">
         <x:v>予算工数</x:v>
@@ -7417,7 +7190,7 @@
         <x:v>String</x:v>
       </x:c>
       <x:c r="F107" s="67" t="str">
-        <x:v>必須</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="G107" s="67" t="str">
         <x:v>最大2000</x:v>
@@ -7426,7 +7199,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="I107" s="67" t="str">
-        <x:v>不可</x:v>
+        <x:v>可</x:v>
       </x:c>
       <x:c r="J107" s="67" t="str">
         <x:v>説明</x:v>
@@ -8170,7 +7943,7 @@
         <x:v>projects.id</x:v>
       </x:c>
     </x:row>
-    <x:row r="129" ht="24" hidden="0" customHeight="1">
+    <x:row r="129" ht="36" hidden="0" customHeight="1">
       <x:c r="A129" s="67" t="str">
         <x:v>API-PRJ-006</x:v>
       </x:c>
@@ -8193,17 +7966,18 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="H129" s="67" t="str">
-        <x:v>PLANNING/IN_PROGRESS/SUSPENDED/COMPLETED/CANCELLED</x:v>
+        <x:v>ACTIVE/LEFT</x:v>
       </x:c>
       <x:c r="I129" s="67" t="str">
         <x:v>可</x:v>
       </x:c>
       <x:c r="J129" s="67" t="str">
-        <x:v>状態</x:v>
+        <x:v>Member状態。省略時ACTIVE。</x:v>
       </x:c>
       <x:c r="K129" s="67" t="str">
-        <x:v>projects.status</x:v>
-      </x:c>
+        <x:v>project_members.status</x:v>
+      </x:c>
+      <x:c r="L129" s="241"/>
     </x:row>
     <x:row r="130" ht="15" hidden="0" customHeight="1">
       <x:c r="A130" s="67" t="str">
@@ -9045,7 +8819,7 @@
         <x:v>project_members.employee_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="154" ht="15" hidden="0" customHeight="1">
+    <x:row r="154" ht="40" hidden="0" customHeight="1">
       <x:c r="A154" s="67" t="str">
         <x:v>API-PRJ-007</x:v>
       </x:c>
@@ -9068,19 +8842,20 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="H154" s="67" t="str">
-        <x:v>PM/MEMBER</x:v>
+        <x:v>MEMBERのみ</x:v>
       </x:c>
       <x:c r="I154" s="67" t="str">
         <x:v>不可</x:v>
       </x:c>
       <x:c r="J154" s="67" t="str">
-        <x:v>Project Role</x:v>
+        <x:v>PM任命はPJ登録/managerId変更で行う。</x:v>
       </x:c>
       <x:c r="K154" s="67" t="str">
         <x:v>project_members.project_role</x:v>
       </x:c>
-    </x:row>
-    <x:row r="155" ht="15" hidden="0" customHeight="1">
+      <x:c r="L154" s="241"/>
+    </x:row>
+    <x:row r="155" ht="40" hidden="0" customHeight="1">
       <x:c r="A155" s="67" t="str">
         <x:v>API-PRJ-007</x:v>
       </x:c>
@@ -9109,11 +8884,12 @@
         <x:v>不可</x:v>
       </x:c>
       <x:c r="J155" s="67" t="str">
-        <x:v>入社日</x:v>
+        <x:v>参加日。操作日JSTと同日必須。予約/遡及不可。</x:v>
       </x:c>
       <x:c r="K155" s="67" t="str">
         <x:v>project_members.joined_date</x:v>
       </x:c>
+      <x:c r="L155" s="241"/>
     </x:row>
     <x:row r="156" ht="15" hidden="0" customHeight="1">
       <x:c r="A156" s="67" t="str">
@@ -9500,7 +9276,7 @@
         <x:v>project_members.employee_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="167" ht="15" hidden="0" customHeight="1">
+    <x:row r="167" ht="65" hidden="0" customHeight="1">
       <x:c r="A167" s="67" t="str">
         <x:v>API-PRJ-008</x:v>
       </x:c>
@@ -9517,58 +9293,36 @@
         <x:v>Integer</x:v>
       </x:c>
       <x:c r="F167" s="67" t="str">
-        <x:v>任意</x:v>
+        <x:v>必須</x:v>
       </x:c>
       <x:c r="G167" s="67" t="str">
-        <x:v>-</x:v>
+        <x:v>0以上の整数</x:v>
       </x:c>
       <x:c r="H167" s="67" t="str">
         <x:v>int32</x:v>
       </x:c>
       <x:c r="I167" s="67" t="str">
-        <x:v>可</x:v>
+        <x:v>不可</x:v>
       </x:c>
       <x:c r="J167" s="67" t="str">
-        <x:v>楽観Lock Version</x:v>
+        <x:v>Version。欠落/Null/形式不正=COMMON-4000、既存対象の不一致=COMMON-4090、削除済/不存在=COMMON-4040。権限確認後に判定。</x:v>
       </x:c>
       <x:c r="K167" s="67" t="str">
         <x:v>projects.version</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="15" hidden="0" customHeight="1">
-      <x:c r="A168" s="67" t="str">
-        <x:v>API-TASK-009</x:v>
-      </x:c>
-      <x:c r="B168" s="67" t="str">
-        <x:v>Request</x:v>
-      </x:c>
-      <x:c r="C168" s="67" t="str">
-        <x:v>path</x:v>
-      </x:c>
-      <x:c r="D168" s="67" t="str">
-        <x:v>request.path.id</x:v>
-      </x:c>
-      <x:c r="E168" s="67" t="str">
-        <x:v>Long</x:v>
-      </x:c>
-      <x:c r="F168" s="67" t="str">
-        <x:v>必須</x:v>
-      </x:c>
-      <x:c r="G168" s="67" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="H168" s="67" t="str">
-        <x:v>int64</x:v>
-      </x:c>
-      <x:c r="I168" s="67" t="str">
-        <x:v>不可</x:v>
-      </x:c>
-      <x:c r="J168" s="67" t="str">
-        <x:v>Task ID</x:v>
-      </x:c>
-      <x:c r="K168" s="67" t="str">
-        <x:v>tasks.id</x:v>
-      </x:c>
+      <x:c r="A168" s="67"/>
+      <x:c r="B168" s="67"/>
+      <x:c r="C168" s="67"/>
+      <x:c r="D168" s="67"/>
+      <x:c r="E168" s="67"/>
+      <x:c r="F168" s="67"/>
+      <x:c r="G168" s="67"/>
+      <x:c r="H168" s="67"/>
+      <x:c r="I168" s="67"/>
+      <x:c r="J168" s="67"/>
+      <x:c r="K168" s="67"/>
     </x:row>
     <x:row r="169" ht="15" hidden="0" customHeight="1">
       <x:c r="A169" s="67" t="str">
@@ -9584,10 +9338,10 @@
         <x:v>response.body</x:v>
       </x:c>
       <x:c r="E169" s="67" t="str">
-        <x:v>Null</x:v>
+        <x:v>Bodyなし</x:v>
       </x:c>
       <x:c r="F169" s="67" t="str">
-        <x:v>任意</x:v>
+        <x:v>送信禁止</x:v>
       </x:c>
       <x:c r="G169" s="67" t="str">
         <x:v>-</x:v>
@@ -9596,10 +9350,10 @@
         <x:v>No Content</x:v>
       </x:c>
       <x:c r="I169" s="67" t="str">
-        <x:v>可</x:v>
+        <x:v>該当なし</x:v>
       </x:c>
       <x:c r="J169" s="67" t="str">
-        <x:v>Response Bodyなし</x:v>
+        <x:v>HTTP 204。JSON null、Envelope、空Objectを送信しない。</x:v>
       </x:c>
       <x:c r="K169" s="67" t="str">
         <x:v>-</x:v>
@@ -9636,25 +9390,60 @@
       <x:c r="J172" s="186"/>
       <x:c r="K172" s="186"/>
     </x:row>
+    <x:row r="173" ht="40" customHeight="1">
+      <x:c r="A173" s="241" t="str">
+        <x:v>API-PRJ-006</x:v>
+      </x:c>
+      <x:c r="B173" s="241" t="str">
+        <x:v>Response</x:v>
+      </x:c>
+      <x:c r="C173" s="241" t="str">
+        <x:v>body</x:v>
+      </x:c>
+      <x:c r="D173" s="241" t="str">
+        <x:v>response.body.data.content[].leftDate</x:v>
+      </x:c>
+      <x:c r="E173" s="241" t="str">
+        <x:v>Date</x:v>
+      </x:c>
+      <x:c r="F173" s="241" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="G173" s="241" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="H173" s="241" t="str">
+        <x:v>yyyy-MM-dd</x:v>
+      </x:c>
+      <x:c r="I173" s="241" t="str">
+        <x:v>可</x:v>
+      </x:c>
+      <x:c r="J173" s="241" t="str">
+        <x:v>離脱日（両端含む）。ACTIVEはNull。</x:v>
+      </x:c>
+      <x:c r="K173" s="241" t="str">
+        <x:v>project_members.left_date</x:v>
+      </x:c>
+      <x:c r="L173" s="241"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:K2"/>
     <x:mergeCell ref="A6:K6"/>
-    <x:mergeCell ref="A163:K164"/>
     <x:mergeCell ref="A171:K172"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="72" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="82" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="100" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="100" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="28" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="38" hidden="0" customWidth="1"/>
@@ -9688,8 +9477,8 @@
         <x:v>Company WorkHub</x:v>
       </x:c>
       <x:c r="C3" s="139"/>
-      <x:c r="D3" s="174" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="D3" s="246" t="str">
+        <x:v>章ID</x:v>
       </x:c>
       <x:c r="E3" s="139" t="str">
         <x:v>CW-BD-12-SAMPLE</x:v>
@@ -9701,18 +9490,29 @@
       <x:c r="A4" s="174" t="str">
         <x:v>版数</x:v>
       </x:c>
-      <x:c r="B4" s="139" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="B4" s="63" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="C4" s="139"/>
       <x:c r="D4" s="174" t="str">
         <x:v>改訂日</x:v>
       </x:c>
-      <x:c r="E4" s="139" t="str">
-        <x:v>2026-08-12</x:v>
+      <x:c r="E4" s="63" t="str">
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="F4" s="139"/>
       <x:c r="G4" s="139"/>
+    </x:row>
+    <x:row r="5" ht="42" customHeight="1">
+      <x:c r="A5" s="203" t="str">
+        <x:v>参考資料。Contract正本は23_API項目定義。Request例は送信区分別の表示用Object（そのまま送るJSONではない）。認証等の共通Headerは10／19参照。Binary PartはFile名で表記。各行は独立した例。</x:v>
+      </x:c>
+      <x:c r="B5" s="203"/>
+      <x:c r="C5" s="203"/>
+      <x:c r="D5" s="203"/>
+      <x:c r="E5" s="203"/>
+      <x:c r="F5" s="203"/>
+      <x:c r="G5" s="203"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="175" t="str">
@@ -9748,7 +9548,7 @@
         <x:v>備考</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="120" customHeight="1">
+    <x:row r="8" ht="115" customHeight="1">
       <x:c r="A8" s="67" t="str">
         <x:v>API-PRJ-001</x:v>
       </x:c>
@@ -9756,54 +9556,10 @@
         <x:v>PJ検索</x:v>
       </x:c>
       <x:c r="C8" s="67" t="str">
-        <x:v>{
-  "query": {
-    "code": "COMMON-0000",
-    "name": "サンプル",
-    "managerId": 1001,
-    "status": "PLANNING",
-    "startFrom": "2026-08-10",
-    "startTo": "2026-08-10",
-    "endFrom": "2026-08-10",
-    "endTo": "2026-08-10",
-    "mine": true,
-    "page": 0,
-    "size": 20,
-    "sort": "sample"
-  }
-}</x:v>
+        <x:v>{"query": {"code": "PJ001", "name": "サンプル", "managerId": 1001, "status": "IN_PROGRESS", "startFrom": "2026-08-10", "startTo": "2026-08-10", "endFrom": "2026-08-10", "endTo": "2026-08-10", "mine": true, "page": 0, "size": 20}}</x:v>
       </x:c>
       <x:c r="D8" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "content": [
-      {
-        "id": 1001,
-        "projectCode": "sample",
-        "name": "サンプル",
-        "managerId": 1001,
-        "managerName": "サンプル",
-        "startDate": "2026-08-10",
-        "endDate": "2026-08-10",
-        "status": "PLANNING",
-        "progress": 50,
-        "memberCount": 1,
-        "taskCount": 1,
-        "version": 1
-      }
-    ],
-    "page": 1,
-    "size": 1,
-    "totalElements": 1001,
-    "totalPages": 1,
-    "first": true,
-    "last": true
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"content": [{"id": 1001, "projectCode": "PJ001", "name": "サンプル", "managerId": 1001, "managerName": "サンプル", "startDate": "2026-08-10", "endDate": "2026-08-10", "status": "IN_PROGRESS", "progress": 50, "memberCount": 1, "taskCount": 2, "version": 1}], "page": 0, "size": 20, "totalElements": 1, "totalPages": 1, "first": true, "last": true}}</x:v>
       </x:c>
       <x:c r="E8" s="67" t="str">
         <x:v>200</x:v>
@@ -9815,7 +9571,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="120" customHeight="1">
+    <x:row r="9" ht="160" customHeight="1">
       <x:c r="A9" s="67" t="str">
         <x:v>API-PRJ-002</x:v>
       </x:c>
@@ -9823,57 +9579,10 @@
         <x:v>PJ詳細</x:v>
       </x:c>
       <x:c r="C9" s="67" t="str">
-        <x:v>{
-  "path": {
-    "id": 1001
-  }
-}</x:v>
+        <x:v>{"path": {"id": 1001}}</x:v>
       </x:c>
       <x:c r="D9" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "id": 1001,
-    "projectCode": "sample",
-    "name": "サンプル",
-    "managerId": 1001,
-    "managerName": "サンプル",
-    "startDate": "2026-08-10",
-    "endDate": "2026-08-10",
-    "status": "PLANNING",
-    "progress": 50,
-    "memberCount": 1,
-    "taskCount": 1,
-    "version": 1,
-    "customerName": "サンプル",
-    "budgetHours": 7.5,
-    "description": "sample",
-    "members": [
-      {
-        "id": 1001,
-        "employeeId": 1001,
-        "employeeCode": "sample",
-        "employeeName": "サンプル",
-        "projectRole": "PM",
-        "joinedDate": "2026-08-10",
-        "status": "ACTIVE",
-        "version": 1
-      }
-    ],
-    "taskSummary": {
-      "total": 42,
-      "todo": 10,
-      "inProgress": 8,
-      "review": 3,
-      "completed": 20,
-      "cancelled": 1,
-      "progress": 68
-    }
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"id": 1001, "projectCode": "sample", "name": "サンプル", "managerId": 1001, "managerName": "サンプル", "startDate": "2026-08-10", "endDate": "2026-08-10", "status": "IN_PROGRESS", "progress": 50, "memberCount": 1, "taskCount": 2, "version": 1, "customerName": "サンプル", "budgetHours": 7.5, "description": "sample", "members": [{"id": 1001, "employeeId": 1001, "employeeCode": "sample", "employeeName": "サンプル", "projectRole": "PM", "joinedDate": "2026-08-10", "status": "ACTIVE", "version": 1}], "taskSummary": {"total": 2, "todo": 0, "inProgress": 1, "review": 0, "completed": 1, "cancelled": 0, "progress": 50}}}</x:v>
       </x:c>
       <x:c r="E9" s="67" t="str">
         <x:v>200</x:v>
@@ -9885,7 +9594,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="120" customHeight="1">
+    <x:row r="10" ht="100" customHeight="1">
       <x:c r="A10" s="67" t="str">
         <x:v>API-PRJ-003</x:v>
       </x:c>
@@ -9893,35 +9602,10 @@
         <x:v>PJ登録</x:v>
       </x:c>
       <x:c r="C10" s="67" t="str">
-        <x:v>{
-  "body": {
-    "projectCode": "sample",
-    "name": "サンプル",
-    "managerId": 1001,
-    "startDate": "2026-08-10",
-    "endDate": "2026-08-10",
-    "status": "PLANNING",
-    "customerName": "サンプル",
-    "budgetHours": 7.5,
-    "description": "sample"
-  },
-  "header": {
-    "X-Idempotency-Key": "550e8400-e29b-41d4-a716-446655440000"
-  }
-}</x:v>
+        <x:v>{"body": {"projectCode": "sample", "name": "サンプル", "managerId": 1001, "startDate": "2026-08-10", "endDate": "2026-08-10", "status": "PLANNING", "customerName": "サンプル", "budgetHours": 7.5, "description": "sample"}, "header": {"X-Idempotency-Key": "550e8400-e29b-41d4-a716-446655440000"}}</x:v>
       </x:c>
       <x:c r="D10" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "id": 1001,
-    "projectCode": "sample",
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"id": 1001, "projectCode": "sample", "version": 1}}</x:v>
       </x:c>
       <x:c r="E10" s="67" t="str">
         <x:v>201</x:v>
@@ -9933,7 +9617,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="120" customHeight="1">
+    <x:row r="11" ht="100" customHeight="1">
       <x:c r="A11" s="67" t="str">
         <x:v>API-PRJ-004</x:v>
       </x:c>
@@ -9941,33 +9625,10 @@
         <x:v>PJ更新</x:v>
       </x:c>
       <x:c r="C11" s="67" t="str">
-        <x:v>{
-  "path": {
-    "id": 1001
-  },
-  "body": {
-    "name": "サンプル",
-    "managerId": 1001,
-    "startDate": "2026-08-10",
-    "endDate": "2026-08-10",
-    "customerName": "サンプル",
-    "budgetHours": 7.5,
-    "description": "sample",
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"path": {"id": 1001}, "body": {"name": "サンプル", "managerId": 1001, "startDate": "2026-08-10", "endDate": "2026-08-10", "customerName": "サンプル", "budgetHours": 7.5, "description": "sample", "version": 1}}</x:v>
       </x:c>
       <x:c r="D11" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "id": 1001,
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"id": 1001, "version": 2}}</x:v>
       </x:c>
       <x:c r="E11" s="67" t="str">
         <x:v>200</x:v>
@@ -9979,7 +9640,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="120" customHeight="1">
+    <x:row r="12" ht="100" customHeight="1">
       <x:c r="A12" s="67" t="str">
         <x:v>API-PRJ-005</x:v>
       </x:c>
@@ -9987,29 +9648,10 @@
         <x:v>PJ状態変更</x:v>
       </x:c>
       <x:c r="C12" s="67" t="str">
-        <x:v>{
-  "path": {
-    "id": 1001
-  },
-  "body": {
-    "status": "PLANNING",
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"path": {"id": 1001}, "body": {"status": "IN_PROGRESS", "version": 1}}</x:v>
       </x:c>
       <x:c r="D12" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "id": 1001,
-    "status": "PLANNING",
-    "progress": 50,
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"id": 1001, "status": "IN_PROGRESS", "progress": 0, "version": 2}}</x:v>
       </x:c>
       <x:c r="E12" s="67" t="str">
         <x:v>200</x:v>
@@ -10018,10 +9660,10 @@
         <x:v>application/json</x:v>
       </x:c>
       <x:c r="G12" s="67" t="str">
-        <x:v>値は例。項目定義を正とする</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="120" customHeight="1">
+        <x:v>例の前提：PJ=PLANNING、Task0件、version=1。開始成功。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="100" customHeight="1">
       <x:c r="A13" s="67" t="str">
         <x:v>API-PRJ-006</x:v>
       </x:c>
@@ -10029,44 +9671,10 @@
         <x:v>Member検索</x:v>
       </x:c>
       <x:c r="C13" s="67" t="str">
-        <x:v>{
-  "path": {
-    "id": 1001
-  },
-  "query": {
-    "status": "PLANNING",
-    "page": 0,
-    "size": 20
-  }
-}</x:v>
+        <x:v>{"path": {"id": 1001}, "query": {"status": "ACTIVE", "page": 0, "size": 20}}</x:v>
       </x:c>
       <x:c r="D13" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "content": [
-      {
-        "id": 1001,
-        "employeeId": 1001,
-        "employeeCode": "sample",
-        "employeeName": "サンプル",
-        "projectRole": "PM",
-        "joinedDate": "2026-08-10",
-        "status": "ACTIVE",
-        "version": 1
-      }
-    ],
-    "page": 1,
-    "size": 1,
-    "totalElements": 1001,
-    "totalPages": 1,
-    "first": true,
-    "last": true
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"content": [{"id": 1001, "employeeId": 1001, "employeeCode": "sample", "employeeName": "サンプル", "projectRole": "PM", "joinedDate": "2026-08-10", "status": "ACTIVE", "version": 1, "leftDate": null}], "page": 0, "size": 20, "totalElements": 1, "totalPages": 1, "first": true, "last": true}}</x:v>
       </x:c>
       <x:c r="E13" s="67" t="str">
         <x:v>200</x:v>
@@ -10078,7 +9686,7 @@
         <x:v>値は例。項目定義を正とする</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="120" customHeight="1">
+    <x:row r="14" ht="100" customHeight="1">
       <x:c r="A14" s="67" t="str">
         <x:v>API-PRJ-007</x:v>
       </x:c>
@@ -10086,32 +9694,10 @@
         <x:v>Member追加</x:v>
       </x:c>
       <x:c r="C14" s="67" t="str">
-        <x:v>{
-  "path": {
-    "id": 1001
-  },
-  "body": {
-    "employeeId": 1001,
-    "projectRole": "PM",
-    "joinedDate": "2026-08-10"
-  },
-  "header": {
-    "X-Idempotency-Key": "550e8400-e29b-41d4-a716-446655440000"
-  }
-}</x:v>
+        <x:v>{"path": {"id": 1001}, "body": {"employeeId": 1001, "projectRole": "MEMBER", "joinedDate": "2026-08-10"}, "header": {"X-Idempotency-Key": "550e8400-e29b-41d4-a716-446655440000"}}</x:v>
       </x:c>
       <x:c r="D14" s="67" t="str">
-        <x:v>{
-  "code": "COMMON-0000",
-  "message": "処理成功",
-  "timestamp": "2026-08-10T10:00:00+09:00",
-  "traceId": "7f3a9c01e2b44d8a",
-  "data": {
-    "id": 1001,
-    "employeeId": 1001,
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"code": "COMMON-0000", "message": "処理成功", "timestamp": "2026-08-10T10:00:00+09:00", "traceId": "7f3a9c01e2b44d8a", "data": {"id": 1001, "employeeId": 1001, "version": 1}}</x:v>
       </x:c>
       <x:c r="E14" s="67" t="str">
         <x:v>201</x:v>
@@ -10120,10 +9706,10 @@
         <x:v>application/json</x:v>
       </x:c>
       <x:c r="G14" s="67" t="str">
-        <x:v>値は例。項目定義を正とする</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="120" customHeight="1">
+        <x:v>値は例。項目定義を正とする。操作日=2026-08-10、社員1001は有効・在籍、未参加、同日離脱履歴なし。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="100" customHeight="1">
       <x:c r="A15" s="67" t="str">
         <x:v>API-PRJ-008</x:v>
       </x:c>
@@ -10131,15 +9717,7 @@
         <x:v>Member削除</x:v>
       </x:c>
       <x:c r="C15" s="67" t="str">
-        <x:v>{
-  "path": {
-    "id": 1001,
-    "employeeId": 1001
-  },
-  "query": {
-    "version": 1
-  }
-}</x:v>
+        <x:v>{"path": {"id": 1001, "employeeId": 1001}, "query": {"version": 1}}</x:v>
       </x:c>
       <x:c r="D15" s="67" t="str">
         <x:v>-（Response Bodyなし）</x:v>
@@ -10151,7 +9729,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G15" s="67" t="str">
-        <x:v>値は例。項目定義を正とする</x:v>
+        <x:v>値は例。項目定義を正とする。社員1001は現PM以外のACTIVE Member、未完了担当Taskなし。</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -10182,284 +9760,4 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="48" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="62" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="138" t="str">
-        <x:v>API権限対応</x:v>
-      </x:c>
-      <x:c r="B1" s="138"/>
-      <x:c r="C1" s="138"/>
-      <x:c r="D1" s="138"/>
-      <x:c r="E1" s="138"/>
-      <x:c r="F1" s="138"/>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="138"/>
-      <x:c r="B2" s="138"/>
-      <x:c r="C2" s="138"/>
-      <x:c r="D2" s="138"/>
-      <x:c r="E2" s="138"/>
-      <x:c r="F2" s="138"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="141" t="str">
-        <x:v>システム名</x:v>
-      </x:c>
-      <x:c r="B3" s="139" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="C3" s="141" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="D3" s="139" t="str">
-        <x:v>CW-BD-12-PERM</x:v>
-      </x:c>
-      <x:c r="E3" s="139"/>
-      <x:c r="F3" s="139"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="141" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="139" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="C4" s="141" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
-      <x:c r="D4" s="139" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
-      <x:c r="E4" s="139"/>
-      <x:c r="F4" s="139"/>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="142" t="str">
-        <x:v>1. API・Permission・Data範囲</x:v>
-      </x:c>
-      <x:c r="B6" s="142"/>
-      <x:c r="C6" s="142"/>
-      <x:c r="D6" s="142"/>
-      <x:c r="E6" s="142"/>
-      <x:c r="F6" s="142"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="147" t="str">
-        <x:v>API ID</x:v>
-      </x:c>
-      <x:c r="B7" s="147" t="str">
-        <x:v>API名</x:v>
-      </x:c>
-      <x:c r="C7" s="147" t="str">
-        <x:v>Permission Code</x:v>
-      </x:c>
-      <x:c r="D7" s="147" t="str">
-        <x:v>許可Role</x:v>
-      </x:c>
-      <x:c r="E7" s="147" t="str">
-        <x:v>Data範囲</x:v>
-      </x:c>
-      <x:c r="F7" s="147" t="str">
-        <x:v>判定方式</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="151" t="str">
-        <x:v>API-PRJ-001</x:v>
-      </x:c>
-      <x:c r="B8" s="151" t="str">
-        <x:v>PJ検索</x:v>
-      </x:c>
-      <x:c r="C8" s="151" t="str">
-        <x:v>PERM-PRJ-READ</x:v>
-      </x:c>
-      <x:c r="D8" s="151" t="str">
-        <x:v>全員</x:v>
-      </x:c>
-      <x:c r="E8" s="151" t="str">
-        <x:v>ADMIN=全社, PM/EMP=担当・参加PJ</x:v>
-      </x:c>
-      <x:c r="F8" s="151" t="str">
-        <x:v>hasAuthority('PERM-PRJ-READ') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="151" t="str">
-        <x:v>API-PRJ-002</x:v>
-      </x:c>
-      <x:c r="B9" s="151" t="str">
-        <x:v>PJ詳細</x:v>
-      </x:c>
-      <x:c r="C9" s="151" t="str">
-        <x:v>PERM-PRJ-READ</x:v>
-      </x:c>
-      <x:c r="D9" s="151" t="str">
-        <x:v>関係者</x:v>
-      </x:c>
-      <x:c r="E9" s="151" t="str">
-        <x:v>ADMINまたはPJ Member</x:v>
-      </x:c>
-      <x:c r="F9" s="151" t="str">
-        <x:v>hasAuthority('PERM-PRJ-READ') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="151" t="str">
-        <x:v>API-PRJ-003</x:v>
-      </x:c>
-      <x:c r="B10" s="151" t="str">
-        <x:v>PJ登録</x:v>
-      </x:c>
-      <x:c r="C10" s="151" t="str">
-        <x:v>PERM-PRJ-WRITE</x:v>
-      </x:c>
-      <x:c r="D10" s="151" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="E10" s="151" t="str">
-        <x:v>管理者のみ</x:v>
-      </x:c>
-      <x:c r="F10" s="151" t="str">
-        <x:v>hasAuthority('PERM-PRJ-WRITE') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="151" t="str">
-        <x:v>API-PRJ-004</x:v>
-      </x:c>
-      <x:c r="B11" s="151" t="str">
-        <x:v>PJ更新</x:v>
-      </x:c>
-      <x:c r="C11" s="151" t="str">
-        <x:v>PERM-PRJ-WRITE</x:v>
-      </x:c>
-      <x:c r="D11" s="151" t="str">
-        <x:v>管理者/担当PM</x:v>
-      </x:c>
-      <x:c r="E11" s="151" t="str">
-        <x:v>ADMINまたは当該PJのPM</x:v>
-      </x:c>
-      <x:c r="F11" s="151" t="str">
-        <x:v>hasAuthority('PERM-PRJ-WRITE') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="151" t="str">
-        <x:v>API-PRJ-005</x:v>
-      </x:c>
-      <x:c r="B12" s="151" t="str">
-        <x:v>PJ状態変更</x:v>
-      </x:c>
-      <x:c r="C12" s="151" t="str">
-        <x:v>PERM-PRJ-WRITE</x:v>
-      </x:c>
-      <x:c r="D12" s="151" t="str">
-        <x:v>管理者/担当PM</x:v>
-      </x:c>
-      <x:c r="E12" s="151" t="str">
-        <x:v>完了時に未完了Taskなし</x:v>
-      </x:c>
-      <x:c r="F12" s="151" t="str">
-        <x:v>hasAuthority('PERM-PRJ-WRITE') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="151" t="str">
-        <x:v>API-PRJ-006</x:v>
-      </x:c>
-      <x:c r="B13" s="151" t="str">
-        <x:v>Member検索</x:v>
-      </x:c>
-      <x:c r="C13" s="151" t="str">
-        <x:v>PERM-PRJ-READ</x:v>
-      </x:c>
-      <x:c r="D13" s="151" t="str">
-        <x:v>関係者</x:v>
-      </x:c>
-      <x:c r="E13" s="151" t="str">
-        <x:v>ADMINまたはPJ Member</x:v>
-      </x:c>
-      <x:c r="F13" s="151" t="str">
-        <x:v>hasAuthority('PERM-PRJ-READ') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="151" t="str">
-        <x:v>API-PRJ-007</x:v>
-      </x:c>
-      <x:c r="B14" s="151" t="str">
-        <x:v>Member追加</x:v>
-      </x:c>
-      <x:c r="C14" s="151" t="str">
-        <x:v>PERM-MEMBER-WRITE</x:v>
-      </x:c>
-      <x:c r="D14" s="151" t="str">
-        <x:v>管理者/担当PM</x:v>
-      </x:c>
-      <x:c r="E14" s="151" t="str">
-        <x:v>ADMINまたは当該PJのPM; 在籍社員</x:v>
-      </x:c>
-      <x:c r="F14" s="151" t="str">
-        <x:v>hasAuthority('PERM-MEMBER-WRITE') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="151" t="str">
-        <x:v>API-PRJ-008</x:v>
-      </x:c>
-      <x:c r="B15" s="151" t="str">
-        <x:v>Member削除</x:v>
-      </x:c>
-      <x:c r="C15" s="151" t="str">
-        <x:v>PERM-MEMBER-WRITE</x:v>
-      </x:c>
-      <x:c r="D15" s="151" t="str">
-        <x:v>管理者/担当PM</x:v>
-      </x:c>
-      <x:c r="E15" s="151" t="str">
-        <x:v>PM・未完了Task担当者は削除不可</x:v>
-      </x:c>
-      <x:c r="F15" s="151" t="str">
-        <x:v>hasAuthority('PERM-MEMBER-WRITE') + Data範囲をServiceで再判定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="155" t="str">
-        <x:v>ControllerのRole表示だけで認可しない。Service層でPermission Code、本人/PJ Member/担当PM等のData範囲、対象Dataの存在を再判定する。</x:v>
-      </x:c>
-      <x:c r="B17" s="155"/>
-      <x:c r="C17" s="155"/>
-      <x:c r="D17" s="155"/>
-      <x:c r="E17" s="155"/>
-      <x:c r="F17" s="155"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="155"/>
-      <x:c r="B18" s="155"/>
-      <x:c r="C18" s="155"/>
-      <x:c r="D18" s="155"/>
-      <x:c r="E18" s="155"/>
-      <x:c r="F18" s="155"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:F2"/>
-    <x:mergeCell ref="A6:F6"/>
-    <x:mergeCell ref="A17:F18"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
 </file>